--- a/ONCHO/Impact Assessments/Eq Guinea/sites.xlsx
+++ b/ONCHO/Impact Assessments/Eq Guinea/sites.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Impact Assessments\Eq Guinea\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{376A1882-C83B-46CD-B47E-E93EAB2D7992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8108EC83-CD1C-473B-BFD4-C5A993F47840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9BD02D18-C695-4CFA-9D63-83A680877932}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9BD02D18-C695-4CFA-9D63-83A680877932}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_Hlk203683618" localSheetId="0">Sheet1!#REF!</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="293">
   <si>
     <t>District</t>
   </si>
@@ -180,13 +183,748 @@
   </si>
   <si>
     <t>Code</t>
+  </si>
+  <si>
+    <t>CAMPO AMOR</t>
+  </si>
+  <si>
+    <t>MBAÑE</t>
+  </si>
+  <si>
+    <t>BORRABECHO</t>
+  </si>
+  <si>
+    <t>BUENOS AIRES</t>
+  </si>
+  <si>
+    <t>ZONA BAJA</t>
+  </si>
+  <si>
+    <t>BASOPU FISTONG</t>
+  </si>
+  <si>
+    <t>VIVIENDAS SOCIALES</t>
+  </si>
+  <si>
+    <t>BARIOBE</t>
+  </si>
+  <si>
+    <t>BAKAKE GRANDE</t>
+  </si>
+  <si>
+    <t>BAKAKE PEQUEÑO</t>
+  </si>
+  <si>
+    <t>COPE</t>
+  </si>
+  <si>
+    <t>ZONA ALTA BASACATO</t>
+  </si>
+  <si>
+    <t>BOSOSO</t>
+  </si>
+  <si>
+    <t>BAO BASUALA</t>
+  </si>
+  <si>
+    <t>BASUALA MISION</t>
+  </si>
+  <si>
+    <t>ZONA BAJA BASACATO</t>
+  </si>
+  <si>
+    <t>BARESO</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO BASAKATO</t>
+  </si>
+  <si>
+    <t>MALABO</t>
+  </si>
+  <si>
+    <t>MADRE BISILA</t>
+  </si>
+  <si>
+    <t>SAMPAKA</t>
+  </si>
+  <si>
+    <t>CAMPO YAOUNDE</t>
+  </si>
+  <si>
+    <t>ARAB CONTRATORS</t>
+  </si>
+  <si>
+    <t>ELA NGUEMA</t>
+  </si>
+  <si>
+    <t>ALEGRE</t>
+  </si>
+  <si>
+    <t>BANEY</t>
+  </si>
+  <si>
+    <t>BUENA ESPERANZA</t>
+  </si>
+  <si>
+    <t>HOSPITAL DE BANEY</t>
+  </si>
+  <si>
+    <t>REBOLA</t>
+  </si>
+  <si>
+    <t>RIO BOSOSO</t>
+  </si>
+  <si>
+    <t>RIO BANEY</t>
+  </si>
+  <si>
+    <t>TOPE BASARICHE</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 1 (CUARTEL MILITAR)</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 1 (ZONA PRESIDENCIAL A)</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 1 (ZONA CATEDRAL)</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 1 MANZANA AA.EE.</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 1 MANZANA CINE JARDÍN Y POLICÍA</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 1 GETESA</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 1 PINTO Y STA TERESITA</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 1 ANTIGUO GEPETROL</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 1 CACHIRULO Y MISIÓN BAUTISTA</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 1 MAGISTERIO</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 1 CÁMARA DE COMERCIO Y ANTIGUO AYUNTAMIENTO</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 1 CALLE PNUD Y BAR BATA</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 1. ZONA PRESIDENCIAL B</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 1 ASAMBLEA DE DIOS Y KELEMA</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 1 DISCOTECA SPORT Y ESCALA 1</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 1 CINE MARFIL</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 1 MANZANA CAYUCO</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 1 MANZANA PDGE Y PALACIO DE JUSTICIA</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 1 MANZANA ANTIGUOS MINISTERIOS</t>
+  </si>
+  <si>
+    <t>AMILIVIA</t>
+  </si>
+  <si>
+    <t>GETRA</t>
+  </si>
+  <si>
+    <t>COMERCIAL SANTY</t>
+  </si>
+  <si>
+    <t>BAR IGLESIA Y LA TOJA</t>
+  </si>
+  <si>
+    <t>IMPECSA</t>
+  </si>
+  <si>
+    <t>MANZANA Mº SANIDAD</t>
+  </si>
+  <si>
+    <t>Mº DE TRABAJO</t>
+  </si>
+  <si>
+    <t>ANTIGUO PIZZA PLACE Y LAYALINA</t>
+  </si>
+  <si>
+    <t>MANZANA BAR PITUSA</t>
+  </si>
+  <si>
+    <t>MINISTRIO DE AGRICULTURA</t>
+  </si>
+  <si>
+    <t>FARMACIA MARISA</t>
+  </si>
+  <si>
+    <t>CRUZ ROJA Y SANTUARIO</t>
+  </si>
+  <si>
+    <t>BARRIO CHINO</t>
+  </si>
+  <si>
+    <t>INSESO Y Mº INFRAESTRUCTURAS</t>
+  </si>
+  <si>
+    <t>CLUB FERNANDINO Y ACACIO MAÑE</t>
+  </si>
+  <si>
+    <t>COIMPEX</t>
+  </si>
+  <si>
+    <t>HOTEL IMPALA</t>
+  </si>
+  <si>
+    <t>LOS ÁNGELES VIUDA JOB 1</t>
+  </si>
+  <si>
+    <t>LOS ÁNGELES VIUDA JOB 2</t>
+  </si>
+  <si>
+    <t>LOS ÁNGELES GETESA 1</t>
+  </si>
+  <si>
+    <t>LOS ÁNGELES GETESA 2</t>
+  </si>
+  <si>
+    <t>LOS ÁNGELES BIFAMILIAR 1</t>
+  </si>
+  <si>
+    <t>LOS ÁNGELES BIFAMILIAR 2</t>
+  </si>
+  <si>
+    <t>LOS ÁNGELES SUGUISA</t>
+  </si>
+  <si>
+    <t>LA PAZ</t>
+  </si>
+  <si>
+    <t>COLASESGA</t>
+  </si>
+  <si>
+    <t>SAW CASTILLO</t>
+  </si>
+  <si>
+    <t>MANZANA EJAPA</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 1.Mº DE AVIACIÓN CIVIL Y CASA BOLA</t>
+  </si>
+  <si>
+    <t>MANZANA HÉROE LUBA Y TIENDA ÁFRICA</t>
+  </si>
+  <si>
+    <t>CCEIBANK Y BAR MIAMI</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO Nº 5</t>
+  </si>
+  <si>
+    <t>PARQUES DE ÁFRICA L</t>
+  </si>
+  <si>
+    <t>PARQUES DE ÁFRICA LL</t>
+  </si>
+  <si>
+    <t>ANTIGUA INDUSTRIA</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO Nº 3 CRUCE HOSPITAL</t>
+  </si>
+  <si>
+    <t>DR. LOERI COMBA L</t>
+  </si>
+  <si>
+    <t>DR. LOERI COMBA LL</t>
+  </si>
+  <si>
+    <t>LAMPERT L</t>
+  </si>
+  <si>
+    <t>LAMPERT LL</t>
+  </si>
+  <si>
+    <t>ALCAIDE L</t>
+  </si>
+  <si>
+    <t>ALCAIDE LL</t>
+  </si>
+  <si>
+    <t>ÁFRICA 2000</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO Nº 5 RIOCOPÚA L</t>
+  </si>
+  <si>
+    <t>RIOCOPÚA LL</t>
+  </si>
+  <si>
+    <t>TIMBABÉ L</t>
+  </si>
+  <si>
+    <t>TIBABÉ LL</t>
+  </si>
+  <si>
+    <t>TIMBABÉ LLL</t>
+  </si>
+  <si>
+    <t>SAMPAKA L</t>
+  </si>
+  <si>
+    <t>SAMPAKA LL</t>
+  </si>
+  <si>
+    <t>SAMPAKA LLL</t>
+  </si>
+  <si>
+    <t>SAMPAKA LV</t>
+  </si>
+  <si>
+    <t>MONGOLA L</t>
+  </si>
+  <si>
+    <t>MONGOLA LL</t>
+  </si>
+  <si>
+    <t>MALABO LL 1</t>
+  </si>
+  <si>
+    <t>MALABO LL 2</t>
+  </si>
+  <si>
+    <t>MALABO LL 3</t>
+  </si>
+  <si>
+    <t>STA MARÍA L</t>
+  </si>
+  <si>
+    <t>STA MARÍA LL 1</t>
+  </si>
+  <si>
+    <t>STA MARÍA LL 2</t>
+  </si>
+  <si>
+    <t>STA MARÍA LLL 1</t>
+  </si>
+  <si>
+    <t>STA MARÍA LLL 2</t>
+  </si>
+  <si>
+    <t>STA MARÍA IV 1</t>
+  </si>
+  <si>
+    <t>STA MARÍA IV 2</t>
+  </si>
+  <si>
+    <t>STA MARÍA IV 3</t>
+  </si>
+  <si>
+    <t>STA MARÍA IV 4</t>
+  </si>
+  <si>
+    <t>STA MARÍA V 1</t>
+  </si>
+  <si>
+    <t>STA MARÍA V 2</t>
+  </si>
+  <si>
+    <t>STA MARÍA V 3</t>
+  </si>
+  <si>
+    <t>PARAÍSO</t>
+  </si>
+  <si>
+    <t>BIABIA</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO DE SACRIBA CACAHUAL</t>
+  </si>
+  <si>
+    <t>POTAO</t>
+  </si>
+  <si>
+    <t>SACRIBA FANG</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 4</t>
+  </si>
+  <si>
+    <t>SERRA</t>
+  </si>
+  <si>
+    <t>PÉREZ 4 POLVORÍN 2</t>
+  </si>
+  <si>
+    <t>PÉREZ 5 CANTERA</t>
+  </si>
+  <si>
+    <t>PÉREZ 1</t>
+  </si>
+  <si>
+    <t>PÉREZ POLVORÍN 1</t>
+  </si>
+  <si>
+    <t>PARROQUIA MARAVILLAS DE JESÚS</t>
+  </si>
+  <si>
+    <t>SAMPAKA V</t>
+  </si>
+  <si>
+    <t>MAGDALENA MORA</t>
+  </si>
+  <si>
+    <t>BUENA ESPERANZA LL</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 4 BANAPÁ 1 AGROPOLIS</t>
+  </si>
+  <si>
+    <t>CAMPO YAOUNDE LLL</t>
+  </si>
+  <si>
+    <t>CAMPO YAOUND LV</t>
+  </si>
+  <si>
+    <t>CAMPO YAOUNDE V</t>
+  </si>
+  <si>
+    <t>CAMPO YAOUNDE VL</t>
+  </si>
+  <si>
+    <t>CAMPO YAOUNDE VLL</t>
+  </si>
+  <si>
+    <t>BIOKO NORTE 1</t>
+  </si>
+  <si>
+    <t>BIOKO NORTE 2</t>
+  </si>
+  <si>
+    <t>BAR MUNDO</t>
+  </si>
+  <si>
+    <t>VIVIENDAS SOCIALES DE BANAPÁ</t>
+  </si>
+  <si>
+    <t>ANTIGUA GAULA</t>
+  </si>
+  <si>
+    <t>BANAPÁ LL</t>
+  </si>
+  <si>
+    <t>OLALA</t>
+  </si>
+  <si>
+    <t>BAR AZUL L</t>
+  </si>
+  <si>
+    <t>BAR AZUL LL</t>
+  </si>
+  <si>
+    <t>VICATANA MAKEDA ZONA A</t>
+  </si>
+  <si>
+    <t>VICATANA MAKEDA ZONA B</t>
+  </si>
+  <si>
+    <t>VICATANA MAKEDA ZONA C</t>
+  </si>
+  <si>
+    <t>VICATANA MAKEDA ZONA D</t>
+  </si>
+  <si>
+    <t>SERVICIO AGRÓNIMO</t>
+  </si>
+  <si>
+    <t>BANAPÁ LLL</t>
+  </si>
+  <si>
+    <t>DETRÁS DE PILAR BUEPOYO</t>
+  </si>
+  <si>
+    <t>CARMEN GALAXY</t>
+  </si>
+  <si>
+    <t>BANAPÁ IV</t>
+  </si>
+  <si>
+    <t>BANAPÁ V</t>
+  </si>
+  <si>
+    <t>NUEVO ESTADIO MALABO</t>
+  </si>
+  <si>
+    <t>CRUCE DRAGAS</t>
+  </si>
+  <si>
+    <t>NKUMABANDA</t>
+  </si>
+  <si>
+    <t>AREA DEL CENTRO DE SALUD CAMPO YAOUNDE ( CUARTEL MILITAR)</t>
+  </si>
+  <si>
+    <t>CAMPO YAOUNDE L</t>
+  </si>
+  <si>
+    <t>CAMPO YAOUNDE LL</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 5</t>
+  </si>
+  <si>
+    <t>STA MARÍA LV 1</t>
+  </si>
+  <si>
+    <t>STA MARÍA LV 2</t>
+  </si>
+  <si>
+    <t>STA MARÍA LV 3</t>
+  </si>
+  <si>
+    <t>STA MARÍA LV 4</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 3</t>
+  </si>
+  <si>
+    <t>SEMU ESCUELA GRADUADA</t>
+  </si>
+  <si>
+    <t>SALOMÉ L</t>
+  </si>
+  <si>
+    <t>SALOMÉ LL</t>
+  </si>
+  <si>
+    <t>FORTUNI L</t>
+  </si>
+  <si>
+    <t>FORTUNI LL</t>
+  </si>
+  <si>
+    <t>FORTUNI LLL</t>
+  </si>
+  <si>
+    <t>FORTUNI LV</t>
+  </si>
+  <si>
+    <t>PORVENIR L</t>
+  </si>
+  <si>
+    <t>PORVENIR LL</t>
+  </si>
+  <si>
+    <t>PORVENIR LLL</t>
+  </si>
+  <si>
+    <t>PORVENIR LV</t>
+  </si>
+  <si>
+    <t>VICATANA (CUARTEL MILITAR)</t>
+  </si>
+  <si>
+    <t>SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>EULOGIO OYO RIQUESA</t>
+  </si>
+  <si>
+    <t>VIVIENDAS SOCIALES DE GEPETROL</t>
+  </si>
+  <si>
+    <t>BEGOÑA LL</t>
+  </si>
+  <si>
+    <t>HACIENDA NATIVIDAD L</t>
+  </si>
+  <si>
+    <t>HACIENDA NATIVIDAD LL</t>
+  </si>
+  <si>
+    <t>CENTRAL TÉRMICA SEMU L</t>
+  </si>
+  <si>
+    <t>CENTRAL TÉRMICA SEMU LL</t>
+  </si>
+  <si>
+    <t>CENTRO EMISORA SEMU</t>
+  </si>
+  <si>
+    <t>SEMU MERCADO</t>
+  </si>
+  <si>
+    <t>SEMU CUARTEL</t>
+  </si>
+  <si>
+    <t>INES NTRA. SEÑORA DEL PILAR L</t>
+  </si>
+  <si>
+    <t>NTRA. SEÑORA DE PILAR LL</t>
+  </si>
+  <si>
+    <t>STO. TOMÁS DE AQUINO</t>
+  </si>
+  <si>
+    <t>ENRIQUE ROCA</t>
+  </si>
+  <si>
+    <t>SAN VALENTÍN L 1</t>
+  </si>
+  <si>
+    <t>SAN VALENTÍN L 2</t>
+  </si>
+  <si>
+    <t>SAN VALENTÍN LL 1</t>
+  </si>
+  <si>
+    <t>SAN JOSÉ</t>
+  </si>
+  <si>
+    <t>SAN VALENTÍN LL 2</t>
+  </si>
+  <si>
+    <t>BASILÉ BUBI</t>
+  </si>
+  <si>
+    <t>DISTRITO URBANO 2</t>
+  </si>
+  <si>
+    <t>MARINA A</t>
+  </si>
+  <si>
+    <t>MARINA B</t>
+  </si>
+  <si>
+    <t>MARINA C</t>
+  </si>
+  <si>
+    <t>PUENTE CALLE BATA L</t>
+  </si>
+  <si>
+    <t>PUENTE CALLE BATA LL</t>
+  </si>
+  <si>
+    <t>PUENTE CALLE BATA LLL</t>
+  </si>
+  <si>
+    <t>MARIA AUXILLADORA</t>
+  </si>
+  <si>
+    <t>CATEDRAL DE ELA NGUEMA</t>
+  </si>
+  <si>
+    <t>FARMACIA EL SALVADOR</t>
+  </si>
+  <si>
+    <t>FISTOWN L</t>
+  </si>
+  <si>
+    <t>FISTOWN LL</t>
+  </si>
+  <si>
+    <t>FISTOWN LLL BALLARES L</t>
+  </si>
+  <si>
+    <t>FISTOWN LLL BALLARES LL</t>
+  </si>
+  <si>
+    <t>COOL WATER L 1</t>
+  </si>
+  <si>
+    <t>COOL WATER L 2</t>
+  </si>
+  <si>
+    <t>COOL WÁTER LL</t>
+  </si>
+  <si>
+    <t>COOL WATER LLL 1</t>
+  </si>
+  <si>
+    <t>COOL WATER LLL 2</t>
+  </si>
+  <si>
+    <t>SUMCO L</t>
+  </si>
+  <si>
+    <t>CINE MAR</t>
+  </si>
+  <si>
+    <t>SUMCO LL</t>
+  </si>
+  <si>
+    <t>SUMCO LLL</t>
+  </si>
+  <si>
+    <t>SUMCO V</t>
+  </si>
+  <si>
+    <t>SUMCO VL</t>
+  </si>
+  <si>
+    <t>SUMCO VLL</t>
+  </si>
+  <si>
+    <t>CUARTEL MARINA</t>
+  </si>
+  <si>
+    <t>BIZINGA L</t>
+  </si>
+  <si>
+    <t>BISINGA LL</t>
+  </si>
+  <si>
+    <t>BISINGA LLL</t>
+  </si>
+  <si>
+    <t>DELEGACIÓN DE GOBIERNO</t>
+  </si>
+  <si>
+    <t>BALOERI</t>
+  </si>
+  <si>
+    <t>BASUPÚ</t>
+  </si>
+  <si>
+    <t>BATOICOPO</t>
+  </si>
+  <si>
+    <t>BERLEYCON NORTE</t>
+  </si>
+  <si>
+    <t>BERLEYCON SUR</t>
+  </si>
+  <si>
+    <t>BOTONOS NORTE</t>
+  </si>
+  <si>
+    <t>BOTONES SUR</t>
+  </si>
+  <si>
+    <t>EL GORRIEGA</t>
+  </si>
+  <si>
+    <t>GRANOS DE ORO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -202,16 +940,52 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -219,18 +993,151 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -571,14 +1478,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F92B2A7F-5160-4E39-8A01-4A2170E2904F}">
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:L286"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="21.5703125" customWidth="1"/>
-    <col min="9" max="9" width="21.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="12"/>
+    <col min="9" max="9" width="21.5703125" style="12" customWidth="1"/>
+    <col min="11" max="12" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -594,14 +1503,20 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="11" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -615,16 +1530,22 @@
         <v>116</v>
       </c>
       <c r="F2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="I2" s="14" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -638,16 +1559,22 @@
         <v>115</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" t="s">
         <v>1</v>
       </c>
-      <c r="I3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H3" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="K3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -660,14 +1587,23 @@
       <c r="D4">
         <v>118</v>
       </c>
-      <c r="H4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="K4" t="s">
+        <v>72</v>
+      </c>
+      <c r="L4" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -680,14 +1616,23 @@
       <c r="D5">
         <v>119</v>
       </c>
-      <c r="H5" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="K5" t="s">
+        <v>72</v>
+      </c>
+      <c r="L5" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -700,14 +1645,20 @@
       <c r="D6">
         <v>104</v>
       </c>
-      <c r="H6" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H6" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="K6" t="s">
+        <v>72</v>
+      </c>
+      <c r="L6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -720,14 +1671,20 @@
       <c r="D7">
         <v>111</v>
       </c>
-      <c r="H7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H7" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="K7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -740,8 +1697,20 @@
       <c r="D8">
         <v>103</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H8" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" t="s">
+        <v>72</v>
+      </c>
+      <c r="L8" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -754,8 +1723,20 @@
       <c r="D9">
         <v>101</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H9" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" t="s">
+        <v>72</v>
+      </c>
+      <c r="L9" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -768,8 +1749,20 @@
       <c r="D10">
         <v>114</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H10" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="K10" t="s">
+        <v>72</v>
+      </c>
+      <c r="L10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -782,8 +1775,20 @@
       <c r="D11">
         <v>105</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H11" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="K11" t="s">
+        <v>72</v>
+      </c>
+      <c r="L11" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -796,8 +1801,20 @@
       <c r="D12">
         <v>113</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H12" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" t="s">
+        <v>70</v>
+      </c>
+      <c r="L12" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1</v>
       </c>
@@ -810,8 +1827,20 @@
       <c r="D13">
         <v>107</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H13" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="K13" t="s">
+        <v>70</v>
+      </c>
+      <c r="L13" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -824,8 +1853,20 @@
       <c r="D14">
         <v>112</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H14" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="K14" t="s">
+        <v>70</v>
+      </c>
+      <c r="L14" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -838,8 +1879,20 @@
       <c r="D15">
         <v>106</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H15" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="K15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L15" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -852,8 +1905,20 @@
       <c r="D16">
         <v>102</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="H16" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="K16" t="s">
+        <v>70</v>
+      </c>
+      <c r="L16" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -866,8 +1931,20 @@
       <c r="D17">
         <v>109</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="H17" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="K17" t="s">
+        <v>70</v>
+      </c>
+      <c r="L17" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1</v>
       </c>
@@ -880,8 +1957,20 @@
       <c r="D18">
         <v>110</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="H18" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="K18" t="s">
+        <v>70</v>
+      </c>
+      <c r="L18" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>1</v>
       </c>
@@ -894,8 +1983,20 @@
       <c r="D19">
         <v>108</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="H19" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19" t="s">
+        <v>70</v>
+      </c>
+      <c r="L19" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -908,8 +2009,14 @@
       <c r="D20">
         <v>120</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K20" t="s">
+        <v>70</v>
+      </c>
+      <c r="L20" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>1</v>
       </c>
@@ -922,8 +2029,14 @@
       <c r="D21">
         <v>117</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K21" t="s">
+        <v>70</v>
+      </c>
+      <c r="L21" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -936,8 +2049,14 @@
       <c r="D22">
         <v>140</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K22" t="s">
+        <v>70</v>
+      </c>
+      <c r="L22" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -950,8 +2069,14 @@
       <c r="D23">
         <v>141</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K23" t="s">
+        <v>70</v>
+      </c>
+      <c r="L23" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -964,8 +2089,14 @@
       <c r="D24">
         <v>124</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K24" t="s">
+        <v>70</v>
+      </c>
+      <c r="L24" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -978,8 +2109,14 @@
       <c r="D25">
         <v>129</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K25" t="s">
+        <v>70</v>
+      </c>
+      <c r="L25" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -992,8 +2129,14 @@
       <c r="D26">
         <v>139</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K26" t="s">
+        <v>70</v>
+      </c>
+      <c r="L26" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -1006,8 +2149,14 @@
       <c r="D27">
         <v>122</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K27" t="s">
+        <v>70</v>
+      </c>
+      <c r="L27" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -1020,8 +2169,14 @@
       <c r="D28">
         <v>132</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K28" t="s">
+        <v>70</v>
+      </c>
+      <c r="L28" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>26</v>
       </c>
@@ -1034,8 +2189,14 @@
       <c r="D29">
         <v>130</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K29" t="s">
+        <v>70</v>
+      </c>
+      <c r="L29" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>26</v>
       </c>
@@ -1048,8 +2209,14 @@
       <c r="D30">
         <v>121</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K30" t="s">
+        <v>70</v>
+      </c>
+      <c r="L30" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>26</v>
       </c>
@@ -1062,8 +2229,14 @@
       <c r="D31">
         <v>123</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K31" t="s">
+        <v>70</v>
+      </c>
+      <c r="L31" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -1076,8 +2249,14 @@
       <c r="D32">
         <v>136</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K32" t="s">
+        <v>70</v>
+      </c>
+      <c r="L32" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>26</v>
       </c>
@@ -1090,8 +2269,14 @@
       <c r="D33">
         <v>137</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K33" t="s">
+        <v>70</v>
+      </c>
+      <c r="L33" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>26</v>
       </c>
@@ -1104,8 +2289,14 @@
       <c r="D34">
         <v>133</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K34" t="s">
+        <v>70</v>
+      </c>
+      <c r="L34" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>26</v>
       </c>
@@ -1118,8 +2309,14 @@
       <c r="D35">
         <v>135</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K35" t="s">
+        <v>70</v>
+      </c>
+      <c r="L35" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>26</v>
       </c>
@@ -1132,8 +2329,14 @@
       <c r="D36">
         <v>138</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K36" t="s">
+        <v>70</v>
+      </c>
+      <c r="L36" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>26</v>
       </c>
@@ -1146,8 +2349,14 @@
       <c r="D37">
         <v>134</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K37" t="s">
+        <v>70</v>
+      </c>
+      <c r="L37" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>26</v>
       </c>
@@ -1160,8 +2369,14 @@
       <c r="D38">
         <v>125</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K38" t="s">
+        <v>70</v>
+      </c>
+      <c r="L38" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>26</v>
       </c>
@@ -1174,8 +2389,14 @@
       <c r="D39">
         <v>131</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K39" t="s">
+        <v>70</v>
+      </c>
+      <c r="L39" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>26</v>
       </c>
@@ -1188,8 +2409,14 @@
       <c r="D40">
         <v>126</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K40" t="s">
+        <v>70</v>
+      </c>
+      <c r="L40" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>26</v>
       </c>
@@ -1202,8 +2429,14 @@
       <c r="D41">
         <v>127</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="K41" t="s">
+        <v>70</v>
+      </c>
+      <c r="L41" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>26</v>
       </c>
@@ -1216,14 +2449,4905 @@
       <c r="D42">
         <v>128</v>
       </c>
+      <c r="K42" t="s">
+        <v>70</v>
+      </c>
+      <c r="L42" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D43">
+        <v>201</v>
+      </c>
+      <c r="K43" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="L43" s="7" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>73</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D44">
+        <v>202</v>
+      </c>
+      <c r="K44" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="L44" s="7" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>73</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D45">
+        <v>203</v>
+      </c>
+      <c r="K45" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="L45" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>73</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D46">
+        <v>204</v>
+      </c>
+      <c r="K46" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>73</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D47">
+        <v>205</v>
+      </c>
+      <c r="K47" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>73</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D48">
+        <v>206</v>
+      </c>
+      <c r="K48" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>73</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D49">
+        <v>207</v>
+      </c>
+      <c r="K49" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>73</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D50">
+        <v>208</v>
+      </c>
+      <c r="K50" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>73</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D51">
+        <v>209</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L51" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>73</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D52">
+        <v>210</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>73</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D53">
+        <v>211</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>73</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D54">
+        <v>212</v>
+      </c>
+      <c r="K54" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>73</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D55">
+        <v>213</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>73</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D56">
+        <v>214</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L56" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>73</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D57">
+        <v>215</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>73</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D58">
+        <v>216</v>
+      </c>
+      <c r="K58" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>73</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D59">
+        <v>217</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>73</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D60">
+        <v>218</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L60" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>73</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D61">
+        <v>219</v>
+      </c>
+      <c r="K61" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>73</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D62">
+        <v>220</v>
+      </c>
+      <c r="K62" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="L62" s="18" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>73</v>
+      </c>
+      <c r="B63" t="s">
+        <v>77</v>
+      </c>
+      <c r="C63" t="s">
+        <v>60</v>
+      </c>
+      <c r="D63">
+        <v>221</v>
+      </c>
+      <c r="K63" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L63" s="17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>73</v>
+      </c>
+      <c r="B64" t="s">
+        <v>78</v>
+      </c>
+      <c r="C64" t="s">
+        <v>79</v>
+      </c>
+      <c r="D64">
+        <v>222</v>
+      </c>
+      <c r="K64" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L64" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>66</v>
+      </c>
+      <c r="B65" t="s">
+        <v>67</v>
+      </c>
+      <c r="C65" t="s">
+        <v>80</v>
+      </c>
+      <c r="D65">
+        <v>223</v>
+      </c>
+      <c r="K65" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L65" s="17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>66</v>
+      </c>
+      <c r="B66" t="s">
+        <v>67</v>
+      </c>
+      <c r="C66" t="s">
+        <v>81</v>
+      </c>
+      <c r="D66">
+        <v>224</v>
+      </c>
+      <c r="K66" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L66" s="17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>67</v>
+      </c>
+      <c r="C67" t="s">
+        <v>82</v>
+      </c>
+      <c r="D67">
+        <v>225</v>
+      </c>
+      <c r="K67" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="L67" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>66</v>
+      </c>
+      <c r="B68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C68" t="s">
+        <v>83</v>
+      </c>
+      <c r="D68">
+        <v>226</v>
+      </c>
+      <c r="K68" t="s">
+        <v>69</v>
+      </c>
+      <c r="L68" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>66</v>
+      </c>
+      <c r="B69" t="s">
+        <v>67</v>
+      </c>
+      <c r="C69" t="s">
+        <v>84</v>
+      </c>
+      <c r="D69">
+        <v>227</v>
+      </c>
+      <c r="K69" t="s">
+        <v>69</v>
+      </c>
+      <c r="L69" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>66</v>
+      </c>
+      <c r="B70" t="s">
+        <v>67</v>
+      </c>
+      <c r="C70" t="s">
+        <v>85</v>
+      </c>
+      <c r="D70">
+        <v>228</v>
+      </c>
+      <c r="K70" t="s">
+        <v>69</v>
+      </c>
+      <c r="L70" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>66</v>
+      </c>
+      <c r="B71" t="s">
+        <v>67</v>
+      </c>
+      <c r="C71" t="s">
+        <v>86</v>
+      </c>
+      <c r="D71">
+        <v>229</v>
+      </c>
+      <c r="K71" t="s">
+        <v>69</v>
+      </c>
+      <c r="L71" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>66</v>
+      </c>
+      <c r="B72" t="s">
+        <v>67</v>
+      </c>
+      <c r="C72" t="s">
+        <v>87</v>
+      </c>
+      <c r="D72">
+        <v>230</v>
+      </c>
+      <c r="K72" t="s">
+        <v>69</v>
+      </c>
+      <c r="L72" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>66</v>
+      </c>
+      <c r="B73" t="s">
+        <v>67</v>
+      </c>
+      <c r="C73" t="s">
+        <v>88</v>
+      </c>
+      <c r="D73">
+        <v>231</v>
+      </c>
+      <c r="K73" t="s">
+        <v>69</v>
+      </c>
+      <c r="L73" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>66</v>
+      </c>
+      <c r="B74" t="s">
+        <v>67</v>
+      </c>
+      <c r="C74" t="s">
+        <v>89</v>
+      </c>
+      <c r="D74">
+        <v>232</v>
+      </c>
+      <c r="K74" t="s">
+        <v>69</v>
+      </c>
+      <c r="L74" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>66</v>
+      </c>
+      <c r="B75" t="s">
+        <v>67</v>
+      </c>
+      <c r="C75" t="s">
+        <v>90</v>
+      </c>
+      <c r="D75">
+        <v>233</v>
+      </c>
+      <c r="K75" t="s">
+        <v>69</v>
+      </c>
+      <c r="L75" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>66</v>
+      </c>
+      <c r="B76" t="s">
+        <v>67</v>
+      </c>
+      <c r="C76" t="s">
+        <v>91</v>
+      </c>
+      <c r="D76">
+        <v>234</v>
+      </c>
+      <c r="K76" t="s">
+        <v>69</v>
+      </c>
+      <c r="L76" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>66</v>
+      </c>
+      <c r="B77" t="s">
+        <v>67</v>
+      </c>
+      <c r="C77" t="s">
+        <v>92</v>
+      </c>
+      <c r="D77">
+        <v>235</v>
+      </c>
+      <c r="K77" t="s">
+        <v>69</v>
+      </c>
+      <c r="L77" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>66</v>
+      </c>
+      <c r="B78" t="s">
+        <v>67</v>
+      </c>
+      <c r="C78" t="s">
+        <v>93</v>
+      </c>
+      <c r="D78">
+        <v>236</v>
+      </c>
+      <c r="K78" t="s">
+        <v>69</v>
+      </c>
+      <c r="L78" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>66</v>
+      </c>
+      <c r="B79" t="s">
+        <v>67</v>
+      </c>
+      <c r="C79" t="s">
+        <v>94</v>
+      </c>
+      <c r="D79">
+        <v>237</v>
+      </c>
+      <c r="K79" t="s">
+        <v>69</v>
+      </c>
+      <c r="L79" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>66</v>
+      </c>
+      <c r="B80" t="s">
+        <v>67</v>
+      </c>
+      <c r="C80" t="s">
+        <v>95</v>
+      </c>
+      <c r="D80">
+        <v>238</v>
+      </c>
+      <c r="K80" t="s">
+        <v>69</v>
+      </c>
+      <c r="L80" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>66</v>
+      </c>
+      <c r="B81" t="s">
+        <v>67</v>
+      </c>
+      <c r="C81" t="s">
+        <v>96</v>
+      </c>
+      <c r="D81">
+        <v>239</v>
+      </c>
+      <c r="K81" t="s">
+        <v>69</v>
+      </c>
+      <c r="L81" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>66</v>
+      </c>
+      <c r="B82" t="s">
+        <v>67</v>
+      </c>
+      <c r="C82" t="s">
+        <v>97</v>
+      </c>
+      <c r="D82">
+        <v>240</v>
+      </c>
+      <c r="K82" t="s">
+        <v>69</v>
+      </c>
+      <c r="L82" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>66</v>
+      </c>
+      <c r="B83" t="s">
+        <v>67</v>
+      </c>
+      <c r="C83" t="s">
+        <v>98</v>
+      </c>
+      <c r="D83">
+        <v>241</v>
+      </c>
+      <c r="K83" t="s">
+        <v>69</v>
+      </c>
+      <c r="L83" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>66</v>
+      </c>
+      <c r="B84" t="s">
+        <v>67</v>
+      </c>
+      <c r="C84" t="s">
+        <v>99</v>
+      </c>
+      <c r="D84">
+        <v>242</v>
+      </c>
+      <c r="K84" t="s">
+        <v>69</v>
+      </c>
+      <c r="L84" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>66</v>
+      </c>
+      <c r="B85" t="s">
+        <v>67</v>
+      </c>
+      <c r="C85" t="s">
+        <v>100</v>
+      </c>
+      <c r="D85">
+        <v>243</v>
+      </c>
+      <c r="K85" t="s">
+        <v>69</v>
+      </c>
+      <c r="L85" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>66</v>
+      </c>
+      <c r="B86" t="s">
+        <v>67</v>
+      </c>
+      <c r="C86" t="s">
+        <v>101</v>
+      </c>
+      <c r="D86">
+        <v>244</v>
+      </c>
+      <c r="K86" t="s">
+        <v>69</v>
+      </c>
+      <c r="L86" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>66</v>
+      </c>
+      <c r="B87" t="s">
+        <v>67</v>
+      </c>
+      <c r="C87" t="s">
+        <v>102</v>
+      </c>
+      <c r="D87">
+        <v>245</v>
+      </c>
+      <c r="K87" t="s">
+        <v>69</v>
+      </c>
+      <c r="L87" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>66</v>
+      </c>
+      <c r="B88" t="s">
+        <v>67</v>
+      </c>
+      <c r="C88" t="s">
+        <v>103</v>
+      </c>
+      <c r="D88">
+        <v>246</v>
+      </c>
+      <c r="K88" t="s">
+        <v>69</v>
+      </c>
+      <c r="L88" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>66</v>
+      </c>
+      <c r="B89" t="s">
+        <v>67</v>
+      </c>
+      <c r="C89" t="s">
+        <v>104</v>
+      </c>
+      <c r="D89">
+        <v>247</v>
+      </c>
+      <c r="K89" t="s">
+        <v>69</v>
+      </c>
+      <c r="L89" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>66</v>
+      </c>
+      <c r="B90" t="s">
+        <v>67</v>
+      </c>
+      <c r="C90" t="s">
+        <v>105</v>
+      </c>
+      <c r="D90">
+        <v>248</v>
+      </c>
+      <c r="K90" t="s">
+        <v>69</v>
+      </c>
+      <c r="L90" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>66</v>
+      </c>
+      <c r="B91" t="s">
+        <v>67</v>
+      </c>
+      <c r="C91" t="s">
+        <v>106</v>
+      </c>
+      <c r="D91">
+        <v>249</v>
+      </c>
+      <c r="K91" t="s">
+        <v>69</v>
+      </c>
+      <c r="L91" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>66</v>
+      </c>
+      <c r="B92" t="s">
+        <v>67</v>
+      </c>
+      <c r="C92" t="s">
+        <v>107</v>
+      </c>
+      <c r="D92">
+        <v>250</v>
+      </c>
+      <c r="K92" t="s">
+        <v>69</v>
+      </c>
+      <c r="L92" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>66</v>
+      </c>
+      <c r="B93" t="s">
+        <v>67</v>
+      </c>
+      <c r="C93" t="s">
+        <v>108</v>
+      </c>
+      <c r="D93">
+        <v>251</v>
+      </c>
+      <c r="K93" t="s">
+        <v>69</v>
+      </c>
+      <c r="L93" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>66</v>
+      </c>
+      <c r="B94" t="s">
+        <v>67</v>
+      </c>
+      <c r="C94" t="s">
+        <v>109</v>
+      </c>
+      <c r="D94">
+        <v>252</v>
+      </c>
+      <c r="K94" t="s">
+        <v>69</v>
+      </c>
+      <c r="L94" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>66</v>
+      </c>
+      <c r="B95" t="s">
+        <v>67</v>
+      </c>
+      <c r="C95" t="s">
+        <v>110</v>
+      </c>
+      <c r="D95">
+        <v>253</v>
+      </c>
+      <c r="K95" t="s">
+        <v>69</v>
+      </c>
+      <c r="L95" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>66</v>
+      </c>
+      <c r="B96" t="s">
+        <v>67</v>
+      </c>
+      <c r="C96" t="s">
+        <v>111</v>
+      </c>
+      <c r="D96">
+        <v>254</v>
+      </c>
+      <c r="K96" t="s">
+        <v>69</v>
+      </c>
+      <c r="L96" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>66</v>
+      </c>
+      <c r="B97" t="s">
+        <v>67</v>
+      </c>
+      <c r="C97" t="s">
+        <v>112</v>
+      </c>
+      <c r="D97">
+        <v>255</v>
+      </c>
+      <c r="K97" t="s">
+        <v>69</v>
+      </c>
+      <c r="L97" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>66</v>
+      </c>
+      <c r="B98" t="s">
+        <v>67</v>
+      </c>
+      <c r="C98" t="s">
+        <v>113</v>
+      </c>
+      <c r="D98">
+        <v>256</v>
+      </c>
+      <c r="K98" t="s">
+        <v>69</v>
+      </c>
+      <c r="L98" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>66</v>
+      </c>
+      <c r="B99" t="s">
+        <v>67</v>
+      </c>
+      <c r="C99" t="s">
+        <v>114</v>
+      </c>
+      <c r="D99">
+        <v>257</v>
+      </c>
+      <c r="K99" t="s">
+        <v>69</v>
+      </c>
+      <c r="L99" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>66</v>
+      </c>
+      <c r="B100" t="s">
+        <v>67</v>
+      </c>
+      <c r="C100" t="s">
+        <v>115</v>
+      </c>
+      <c r="D100">
+        <v>258</v>
+      </c>
+      <c r="K100" t="s">
+        <v>69</v>
+      </c>
+      <c r="L100" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>66</v>
+      </c>
+      <c r="B101" t="s">
+        <v>67</v>
+      </c>
+      <c r="C101" t="s">
+        <v>116</v>
+      </c>
+      <c r="D101">
+        <v>259</v>
+      </c>
+      <c r="K101" t="s">
+        <v>69</v>
+      </c>
+      <c r="L101" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>66</v>
+      </c>
+      <c r="B102" t="s">
+        <v>67</v>
+      </c>
+      <c r="C102" t="s">
+        <v>117</v>
+      </c>
+      <c r="D102">
+        <v>260</v>
+      </c>
+      <c r="K102" t="s">
+        <v>69</v>
+      </c>
+      <c r="L102" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>66</v>
+      </c>
+      <c r="B103" t="s">
+        <v>67</v>
+      </c>
+      <c r="C103" t="s">
+        <v>118</v>
+      </c>
+      <c r="D103">
+        <v>261</v>
+      </c>
+      <c r="K103" t="s">
+        <v>69</v>
+      </c>
+      <c r="L103" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>66</v>
+      </c>
+      <c r="B104" t="s">
+        <v>67</v>
+      </c>
+      <c r="C104" t="s">
+        <v>119</v>
+      </c>
+      <c r="D104">
+        <v>262</v>
+      </c>
+      <c r="K104" t="s">
+        <v>69</v>
+      </c>
+      <c r="L104" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>66</v>
+      </c>
+      <c r="B105" t="s">
+        <v>67</v>
+      </c>
+      <c r="C105" t="s">
+        <v>120</v>
+      </c>
+      <c r="D105">
+        <v>263</v>
+      </c>
+      <c r="K105" t="s">
+        <v>69</v>
+      </c>
+      <c r="L105" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>66</v>
+      </c>
+      <c r="B106" t="s">
+        <v>67</v>
+      </c>
+      <c r="C106" t="s">
+        <v>121</v>
+      </c>
+      <c r="D106">
+        <v>264</v>
+      </c>
+      <c r="K106" t="s">
+        <v>69</v>
+      </c>
+      <c r="L106" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>66</v>
+      </c>
+      <c r="B107" t="s">
+        <v>67</v>
+      </c>
+      <c r="C107" t="s">
+        <v>122</v>
+      </c>
+      <c r="D107">
+        <v>265</v>
+      </c>
+      <c r="K107" t="s">
+        <v>69</v>
+      </c>
+      <c r="L107" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>66</v>
+      </c>
+      <c r="B108" t="s">
+        <v>67</v>
+      </c>
+      <c r="C108" t="s">
+        <v>123</v>
+      </c>
+      <c r="D108">
+        <v>266</v>
+      </c>
+      <c r="K108" t="s">
+        <v>69</v>
+      </c>
+      <c r="L108" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>66</v>
+      </c>
+      <c r="B109" t="s">
+        <v>67</v>
+      </c>
+      <c r="C109" t="s">
+        <v>124</v>
+      </c>
+      <c r="D109">
+        <v>267</v>
+      </c>
+      <c r="K109" t="s">
+        <v>69</v>
+      </c>
+      <c r="L109" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>66</v>
+      </c>
+      <c r="B110" t="s">
+        <v>67</v>
+      </c>
+      <c r="C110" t="s">
+        <v>125</v>
+      </c>
+      <c r="D110">
+        <v>268</v>
+      </c>
+      <c r="K110" t="s">
+        <v>69</v>
+      </c>
+      <c r="L110" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>66</v>
+      </c>
+      <c r="B111" t="s">
+        <v>67</v>
+      </c>
+      <c r="C111" t="s">
+        <v>126</v>
+      </c>
+      <c r="D111">
+        <v>269</v>
+      </c>
+      <c r="K111" t="s">
+        <v>69</v>
+      </c>
+      <c r="L111" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>66</v>
+      </c>
+      <c r="B112" t="s">
+        <v>67</v>
+      </c>
+      <c r="C112" t="s">
+        <v>127</v>
+      </c>
+      <c r="D112">
+        <v>270</v>
+      </c>
+      <c r="K112" t="s">
+        <v>71</v>
+      </c>
+      <c r="L112" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>66</v>
+      </c>
+      <c r="B113" t="s">
+        <v>67</v>
+      </c>
+      <c r="C113" t="s">
+        <v>128</v>
+      </c>
+      <c r="D113">
+        <v>271</v>
+      </c>
+      <c r="K113" t="s">
+        <v>71</v>
+      </c>
+      <c r="L113" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>66</v>
+      </c>
+      <c r="B114" t="s">
+        <v>67</v>
+      </c>
+      <c r="C114" t="s">
+        <v>129</v>
+      </c>
+      <c r="D114">
+        <v>272</v>
+      </c>
+      <c r="K114" t="s">
+        <v>71</v>
+      </c>
+      <c r="L114" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>66</v>
+      </c>
+      <c r="B115" t="s">
+        <v>67</v>
+      </c>
+      <c r="C115" t="s">
+        <v>130</v>
+      </c>
+      <c r="D115">
+        <v>273</v>
+      </c>
+      <c r="K115" t="s">
+        <v>71</v>
+      </c>
+      <c r="L115" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>66</v>
+      </c>
+      <c r="B116" t="s">
+        <v>67</v>
+      </c>
+      <c r="C116" t="s">
+        <v>131</v>
+      </c>
+      <c r="D116">
+        <v>274</v>
+      </c>
+      <c r="K116" t="s">
+        <v>71</v>
+      </c>
+      <c r="L116" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>66</v>
+      </c>
+      <c r="B117" t="s">
+        <v>67</v>
+      </c>
+      <c r="C117" t="s">
+        <v>132</v>
+      </c>
+      <c r="D117">
+        <v>275</v>
+      </c>
+      <c r="K117" t="s">
+        <v>71</v>
+      </c>
+      <c r="L117" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>66</v>
+      </c>
+      <c r="B118" t="s">
+        <v>67</v>
+      </c>
+      <c r="C118" t="s">
+        <v>133</v>
+      </c>
+      <c r="D118">
+        <v>276</v>
+      </c>
+      <c r="K118" t="s">
+        <v>71</v>
+      </c>
+      <c r="L118" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>66</v>
+      </c>
+      <c r="B119" t="s">
+        <v>67</v>
+      </c>
+      <c r="C119" t="s">
+        <v>134</v>
+      </c>
+      <c r="D119">
+        <v>277</v>
+      </c>
+      <c r="K119" t="s">
+        <v>71</v>
+      </c>
+      <c r="L119" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>66</v>
+      </c>
+      <c r="B120" t="s">
+        <v>67</v>
+      </c>
+      <c r="C120" t="s">
+        <v>135</v>
+      </c>
+      <c r="D120">
+        <v>278</v>
+      </c>
+      <c r="K120" t="s">
+        <v>71</v>
+      </c>
+      <c r="L120" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>66</v>
+      </c>
+      <c r="B121" t="s">
+        <v>67</v>
+      </c>
+      <c r="C121" t="s">
+        <v>136</v>
+      </c>
+      <c r="D121">
+        <v>279</v>
+      </c>
+      <c r="K121" t="s">
+        <v>71</v>
+      </c>
+      <c r="L121" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>66</v>
+      </c>
+      <c r="B122" t="s">
+        <v>67</v>
+      </c>
+      <c r="C122" t="s">
+        <v>137</v>
+      </c>
+      <c r="D122">
+        <v>280</v>
+      </c>
+      <c r="K122" t="s">
+        <v>71</v>
+      </c>
+      <c r="L122" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>66</v>
+      </c>
+      <c r="B123" t="s">
+        <v>67</v>
+      </c>
+      <c r="C123" t="s">
+        <v>138</v>
+      </c>
+      <c r="D123">
+        <v>281</v>
+      </c>
+      <c r="K123" t="s">
+        <v>71</v>
+      </c>
+      <c r="L123" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>66</v>
+      </c>
+      <c r="B124" t="s">
+        <v>67</v>
+      </c>
+      <c r="C124" t="s">
+        <v>139</v>
+      </c>
+      <c r="D124">
+        <v>282</v>
+      </c>
+      <c r="K124" t="s">
+        <v>71</v>
+      </c>
+      <c r="L124" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>66</v>
+      </c>
+      <c r="B125" t="s">
+        <v>67</v>
+      </c>
+      <c r="C125" t="s">
+        <v>140</v>
+      </c>
+      <c r="D125">
+        <v>283</v>
+      </c>
+      <c r="K125" t="s">
+        <v>71</v>
+      </c>
+      <c r="L125" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>66</v>
+      </c>
+      <c r="B126" t="s">
+        <v>67</v>
+      </c>
+      <c r="C126" t="s">
+        <v>141</v>
+      </c>
+      <c r="D126">
+        <v>284</v>
+      </c>
+      <c r="K126" t="s">
+        <v>71</v>
+      </c>
+      <c r="L126" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>66</v>
+      </c>
+      <c r="B127" t="s">
+        <v>68</v>
+      </c>
+      <c r="C127" t="s">
+        <v>142</v>
+      </c>
+      <c r="D127">
+        <v>285</v>
+      </c>
+      <c r="K127" t="s">
+        <v>71</v>
+      </c>
+      <c r="L127" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>66</v>
+      </c>
+      <c r="B128" t="s">
+        <v>68</v>
+      </c>
+      <c r="C128" t="s">
+        <v>143</v>
+      </c>
+      <c r="D128">
+        <v>286</v>
+      </c>
+      <c r="K128" t="s">
+        <v>71</v>
+      </c>
+      <c r="L128" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>66</v>
+      </c>
+      <c r="B129" t="s">
+        <v>68</v>
+      </c>
+      <c r="C129" t="s">
+        <v>144</v>
+      </c>
+      <c r="D129">
+        <v>287</v>
+      </c>
+      <c r="K129" t="s">
+        <v>71</v>
+      </c>
+      <c r="L129" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>66</v>
+      </c>
+      <c r="B130" t="s">
+        <v>68</v>
+      </c>
+      <c r="C130" t="s">
+        <v>145</v>
+      </c>
+      <c r="D130">
+        <v>288</v>
+      </c>
+      <c r="K130" t="s">
+        <v>71</v>
+      </c>
+      <c r="L130" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>66</v>
+      </c>
+      <c r="B131" t="s">
+        <v>68</v>
+      </c>
+      <c r="C131" t="s">
+        <v>146</v>
+      </c>
+      <c r="D131">
+        <v>289</v>
+      </c>
+      <c r="K131" t="s">
+        <v>71</v>
+      </c>
+      <c r="L131" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>66</v>
+      </c>
+      <c r="B132" t="s">
+        <v>68</v>
+      </c>
+      <c r="C132" t="s">
+        <v>147</v>
+      </c>
+      <c r="D132">
+        <v>290</v>
+      </c>
+      <c r="K132" t="s">
+        <v>71</v>
+      </c>
+      <c r="L132" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>66</v>
+      </c>
+      <c r="B133" t="s">
+        <v>68</v>
+      </c>
+      <c r="C133" t="s">
+        <v>148</v>
+      </c>
+      <c r="D133">
+        <v>291</v>
+      </c>
+      <c r="K133" t="s">
+        <v>71</v>
+      </c>
+      <c r="L133" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>66</v>
+      </c>
+      <c r="B134" t="s">
+        <v>68</v>
+      </c>
+      <c r="C134" t="s">
+        <v>149</v>
+      </c>
+      <c r="D134">
+        <v>292</v>
+      </c>
+      <c r="K134" t="s">
+        <v>71</v>
+      </c>
+      <c r="L134" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>66</v>
+      </c>
+      <c r="B135" t="s">
+        <v>68</v>
+      </c>
+      <c r="C135" t="s">
+        <v>150</v>
+      </c>
+      <c r="D135">
+        <v>293</v>
+      </c>
+      <c r="K135" t="s">
+        <v>71</v>
+      </c>
+      <c r="L135" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>66</v>
+      </c>
+      <c r="B136" t="s">
+        <v>68</v>
+      </c>
+      <c r="C136" t="s">
+        <v>151</v>
+      </c>
+      <c r="D136">
+        <v>294</v>
+      </c>
+      <c r="K136" t="s">
+        <v>71</v>
+      </c>
+      <c r="L136" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>66</v>
+      </c>
+      <c r="B137" t="s">
+        <v>68</v>
+      </c>
+      <c r="C137" t="s">
+        <v>152</v>
+      </c>
+      <c r="D137">
+        <v>295</v>
+      </c>
+      <c r="K137" t="s">
+        <v>71</v>
+      </c>
+      <c r="L137" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>66</v>
+      </c>
+      <c r="B138" t="s">
+        <v>68</v>
+      </c>
+      <c r="C138" t="s">
+        <v>153</v>
+      </c>
+      <c r="D138">
+        <v>296</v>
+      </c>
+      <c r="K138" t="s">
+        <v>71</v>
+      </c>
+      <c r="L138" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>66</v>
+      </c>
+      <c r="B139" t="s">
+        <v>68</v>
+      </c>
+      <c r="C139" t="s">
+        <v>154</v>
+      </c>
+      <c r="D139">
+        <v>297</v>
+      </c>
+      <c r="K139" t="s">
+        <v>71</v>
+      </c>
+      <c r="L139" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>66</v>
+      </c>
+      <c r="B140" t="s">
+        <v>68</v>
+      </c>
+      <c r="C140" t="s">
+        <v>155</v>
+      </c>
+      <c r="D140">
+        <v>298</v>
+      </c>
+      <c r="K140" t="s">
+        <v>71</v>
+      </c>
+      <c r="L140" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>66</v>
+      </c>
+      <c r="B141" t="s">
+        <v>68</v>
+      </c>
+      <c r="C141" t="s">
+        <v>156</v>
+      </c>
+      <c r="D141">
+        <v>299</v>
+      </c>
+      <c r="K141" t="s">
+        <v>71</v>
+      </c>
+      <c r="L141" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>66</v>
+      </c>
+      <c r="B142" t="s">
+        <v>68</v>
+      </c>
+      <c r="C142" t="s">
+        <v>157</v>
+      </c>
+      <c r="D142">
+        <v>300</v>
+      </c>
+      <c r="K142" t="s">
+        <v>71</v>
+      </c>
+      <c r="L142" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>66</v>
+      </c>
+      <c r="B143" t="s">
+        <v>68</v>
+      </c>
+      <c r="C143" t="s">
+        <v>158</v>
+      </c>
+      <c r="D143">
+        <v>301</v>
+      </c>
+      <c r="K143" t="s">
+        <v>4</v>
+      </c>
+      <c r="L143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>66</v>
+      </c>
+      <c r="B144" t="s">
+        <v>68</v>
+      </c>
+      <c r="C144" t="s">
+        <v>159</v>
+      </c>
+      <c r="D144">
+        <v>302</v>
+      </c>
+      <c r="K144" t="s">
+        <v>4</v>
+      </c>
+      <c r="L144" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>66</v>
+      </c>
+      <c r="B145" t="s">
+        <v>68</v>
+      </c>
+      <c r="C145" t="s">
+        <v>160</v>
+      </c>
+      <c r="D145">
+        <v>303</v>
+      </c>
+      <c r="K145" t="s">
+        <v>4</v>
+      </c>
+      <c r="L145" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>66</v>
+      </c>
+      <c r="B146" t="s">
+        <v>68</v>
+      </c>
+      <c r="C146" t="s">
+        <v>161</v>
+      </c>
+      <c r="D146">
+        <v>304</v>
+      </c>
+      <c r="K146" t="s">
+        <v>4</v>
+      </c>
+      <c r="L146" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>66</v>
+      </c>
+      <c r="B147" t="s">
+        <v>68</v>
+      </c>
+      <c r="C147" t="s">
+        <v>162</v>
+      </c>
+      <c r="D147">
+        <v>305</v>
+      </c>
+      <c r="K147" t="s">
+        <v>4</v>
+      </c>
+      <c r="L147" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>66</v>
+      </c>
+      <c r="B148" t="s">
+        <v>68</v>
+      </c>
+      <c r="C148" t="s">
+        <v>163</v>
+      </c>
+      <c r="D148">
+        <v>306</v>
+      </c>
+      <c r="K148" t="s">
+        <v>4</v>
+      </c>
+      <c r="L148" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>66</v>
+      </c>
+      <c r="B149" t="s">
+        <v>68</v>
+      </c>
+      <c r="C149" t="s">
+        <v>164</v>
+      </c>
+      <c r="D149">
+        <v>307</v>
+      </c>
+      <c r="K149" t="s">
+        <v>4</v>
+      </c>
+      <c r="L149" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>66</v>
+      </c>
+      <c r="B150" t="s">
+        <v>68</v>
+      </c>
+      <c r="C150" t="s">
+        <v>165</v>
+      </c>
+      <c r="D150">
+        <v>308</v>
+      </c>
+      <c r="K150" t="s">
+        <v>4</v>
+      </c>
+      <c r="L150" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>66</v>
+      </c>
+      <c r="B151" t="s">
+        <v>68</v>
+      </c>
+      <c r="C151" t="s">
+        <v>166</v>
+      </c>
+      <c r="D151">
+        <v>309</v>
+      </c>
+      <c r="K151" t="s">
+        <v>4</v>
+      </c>
+      <c r="L151" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>66</v>
+      </c>
+      <c r="B152" t="s">
+        <v>68</v>
+      </c>
+      <c r="C152" t="s">
+        <v>167</v>
+      </c>
+      <c r="D152">
+        <v>310</v>
+      </c>
+      <c r="K152" t="s">
+        <v>4</v>
+      </c>
+      <c r="L152" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>66</v>
+      </c>
+      <c r="B153" t="s">
+        <v>68</v>
+      </c>
+      <c r="C153" t="s">
+        <v>168</v>
+      </c>
+      <c r="D153">
+        <v>311</v>
+      </c>
+      <c r="K153" t="s">
+        <v>4</v>
+      </c>
+      <c r="L153" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>66</v>
+      </c>
+      <c r="B154" t="s">
+        <v>68</v>
+      </c>
+      <c r="C154" t="s">
+        <v>169</v>
+      </c>
+      <c r="D154">
+        <v>312</v>
+      </c>
+      <c r="K154" t="s">
+        <v>4</v>
+      </c>
+      <c r="L154" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>66</v>
+      </c>
+      <c r="B155" t="s">
+        <v>68</v>
+      </c>
+      <c r="C155" t="s">
+        <v>170</v>
+      </c>
+      <c r="D155">
+        <v>313</v>
+      </c>
+      <c r="K155" t="s">
+        <v>4</v>
+      </c>
+      <c r="L155" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>66</v>
+      </c>
+      <c r="B156" t="s">
+        <v>68</v>
+      </c>
+      <c r="C156" t="s">
+        <v>171</v>
+      </c>
+      <c r="D156">
+        <v>314</v>
+      </c>
+      <c r="K156" t="s">
+        <v>4</v>
+      </c>
+      <c r="L156" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>66</v>
+      </c>
+      <c r="B157" t="s">
+        <v>68</v>
+      </c>
+      <c r="C157" t="s">
+        <v>172</v>
+      </c>
+      <c r="D157">
+        <v>315</v>
+      </c>
+      <c r="K157" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="L157" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>66</v>
+      </c>
+      <c r="B158" t="s">
+        <v>68</v>
+      </c>
+      <c r="C158" t="s">
+        <v>173</v>
+      </c>
+      <c r="D158">
+        <v>316</v>
+      </c>
+      <c r="K158" t="s">
+        <v>67</v>
+      </c>
+      <c r="L158" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>66</v>
+      </c>
+      <c r="B159" t="s">
+        <v>68</v>
+      </c>
+      <c r="C159" t="s">
+        <v>174</v>
+      </c>
+      <c r="D159">
+        <v>317</v>
+      </c>
+      <c r="K159" t="s">
+        <v>67</v>
+      </c>
+      <c r="L159" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>66</v>
+      </c>
+      <c r="B160" t="s">
+        <v>68</v>
+      </c>
+      <c r="C160" t="s">
+        <v>175</v>
+      </c>
+      <c r="D160">
+        <v>318</v>
+      </c>
+      <c r="K160" t="s">
+        <v>67</v>
+      </c>
+      <c r="L160" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>66</v>
+      </c>
+      <c r="B161" t="s">
+        <v>68</v>
+      </c>
+      <c r="C161" t="s">
+        <v>176</v>
+      </c>
+      <c r="D161">
+        <v>319</v>
+      </c>
+      <c r="K161" t="s">
+        <v>67</v>
+      </c>
+      <c r="L161" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>66</v>
+      </c>
+      <c r="B162" t="s">
+        <v>68</v>
+      </c>
+      <c r="C162" t="s">
+        <v>177</v>
+      </c>
+      <c r="D162">
+        <v>320</v>
+      </c>
+      <c r="K162" t="s">
+        <v>67</v>
+      </c>
+      <c r="L162" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>66</v>
+      </c>
+      <c r="B163" t="s">
+        <v>68</v>
+      </c>
+      <c r="C163" t="s">
+        <v>178</v>
+      </c>
+      <c r="D163">
+        <v>321</v>
+      </c>
+      <c r="K163" t="s">
+        <v>67</v>
+      </c>
+      <c r="L163" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>66</v>
+      </c>
+      <c r="B164" t="s">
+        <v>68</v>
+      </c>
+      <c r="C164" t="s">
+        <v>179</v>
+      </c>
+      <c r="D164">
+        <v>322</v>
+      </c>
+      <c r="K164" t="s">
+        <v>67</v>
+      </c>
+      <c r="L164" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>66</v>
+      </c>
+      <c r="B165" t="s">
+        <v>68</v>
+      </c>
+      <c r="C165" t="s">
+        <v>180</v>
+      </c>
+      <c r="D165">
+        <v>323</v>
+      </c>
+      <c r="K165" t="s">
+        <v>67</v>
+      </c>
+      <c r="L165" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>66</v>
+      </c>
+      <c r="B166" t="s">
+        <v>68</v>
+      </c>
+      <c r="C166" t="s">
+        <v>181</v>
+      </c>
+      <c r="D166">
+        <v>324</v>
+      </c>
+      <c r="K166" t="s">
+        <v>67</v>
+      </c>
+      <c r="L166" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>66</v>
+      </c>
+      <c r="B167" t="s">
+        <v>68</v>
+      </c>
+      <c r="C167" t="s">
+        <v>182</v>
+      </c>
+      <c r="D167">
+        <v>325</v>
+      </c>
+      <c r="K167" t="s">
+        <v>67</v>
+      </c>
+      <c r="L167" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>66</v>
+      </c>
+      <c r="B168" t="s">
+        <v>69</v>
+      </c>
+      <c r="C168" t="s">
+        <v>183</v>
+      </c>
+      <c r="D168">
+        <v>326</v>
+      </c>
+      <c r="K168" t="s">
+        <v>67</v>
+      </c>
+      <c r="L168" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>66</v>
+      </c>
+      <c r="B169" t="s">
+        <v>69</v>
+      </c>
+      <c r="C169" t="s">
+        <v>184</v>
+      </c>
+      <c r="D169">
+        <v>327</v>
+      </c>
+      <c r="K169" t="s">
+        <v>67</v>
+      </c>
+      <c r="L169" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>66</v>
+      </c>
+      <c r="B170" t="s">
+        <v>69</v>
+      </c>
+      <c r="C170" t="s">
+        <v>185</v>
+      </c>
+      <c r="D170">
+        <v>328</v>
+      </c>
+      <c r="K170" t="s">
+        <v>67</v>
+      </c>
+      <c r="L170" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>66</v>
+      </c>
+      <c r="B171" t="s">
+        <v>69</v>
+      </c>
+      <c r="C171" t="s">
+        <v>186</v>
+      </c>
+      <c r="D171">
+        <v>329</v>
+      </c>
+      <c r="K171" t="s">
+        <v>67</v>
+      </c>
+      <c r="L171" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>66</v>
+      </c>
+      <c r="B172" t="s">
+        <v>69</v>
+      </c>
+      <c r="C172" t="s">
+        <v>187</v>
+      </c>
+      <c r="D172">
+        <v>330</v>
+      </c>
+      <c r="K172" t="s">
+        <v>67</v>
+      </c>
+      <c r="L172" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>66</v>
+      </c>
+      <c r="B173" t="s">
+        <v>69</v>
+      </c>
+      <c r="C173" t="s">
+        <v>188</v>
+      </c>
+      <c r="D173">
+        <v>331</v>
+      </c>
+      <c r="K173" t="s">
+        <v>67</v>
+      </c>
+      <c r="L173" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>66</v>
+      </c>
+      <c r="B174" t="s">
+        <v>69</v>
+      </c>
+      <c r="C174" t="s">
+        <v>189</v>
+      </c>
+      <c r="D174">
+        <v>332</v>
+      </c>
+      <c r="K174" t="s">
+        <v>67</v>
+      </c>
+      <c r="L174" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>66</v>
+      </c>
+      <c r="B175" t="s">
+        <v>69</v>
+      </c>
+      <c r="C175" t="s">
+        <v>190</v>
+      </c>
+      <c r="D175">
+        <v>333</v>
+      </c>
+      <c r="K175" t="s">
+        <v>67</v>
+      </c>
+      <c r="L175" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>66</v>
+      </c>
+      <c r="B176" t="s">
+        <v>69</v>
+      </c>
+      <c r="C176" t="s">
+        <v>191</v>
+      </c>
+      <c r="D176">
+        <v>334</v>
+      </c>
+      <c r="K176" t="s">
+        <v>67</v>
+      </c>
+      <c r="L176" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>66</v>
+      </c>
+      <c r="B177" t="s">
+        <v>69</v>
+      </c>
+      <c r="C177" t="s">
+        <v>192</v>
+      </c>
+      <c r="D177">
+        <v>335</v>
+      </c>
+      <c r="K177" t="s">
+        <v>67</v>
+      </c>
+      <c r="L177" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>66</v>
+      </c>
+      <c r="B178" t="s">
+        <v>69</v>
+      </c>
+      <c r="C178" t="s">
+        <v>193</v>
+      </c>
+      <c r="D178">
+        <v>336</v>
+      </c>
+      <c r="K178" t="s">
+        <v>67</v>
+      </c>
+      <c r="L178" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>66</v>
+      </c>
+      <c r="B179" t="s">
+        <v>69</v>
+      </c>
+      <c r="C179" t="s">
+        <v>194</v>
+      </c>
+      <c r="D179">
+        <v>337</v>
+      </c>
+      <c r="K179" t="s">
+        <v>67</v>
+      </c>
+      <c r="L179" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>66</v>
+      </c>
+      <c r="B180" t="s">
+        <v>69</v>
+      </c>
+      <c r="C180" t="s">
+        <v>195</v>
+      </c>
+      <c r="D180">
+        <v>338</v>
+      </c>
+      <c r="K180" t="s">
+        <v>67</v>
+      </c>
+      <c r="L180" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>66</v>
+      </c>
+      <c r="B181" t="s">
+        <v>69</v>
+      </c>
+      <c r="C181" t="s">
+        <v>196</v>
+      </c>
+      <c r="D181">
+        <v>339</v>
+      </c>
+      <c r="K181" t="s">
+        <v>67</v>
+      </c>
+      <c r="L181" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>66</v>
+      </c>
+      <c r="B182" t="s">
+        <v>69</v>
+      </c>
+      <c r="C182" t="s">
+        <v>197</v>
+      </c>
+      <c r="D182">
+        <v>340</v>
+      </c>
+      <c r="K182" t="s">
+        <v>67</v>
+      </c>
+      <c r="L182" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>66</v>
+      </c>
+      <c r="B183" t="s">
+        <v>69</v>
+      </c>
+      <c r="C183" t="s">
+        <v>198</v>
+      </c>
+      <c r="D183">
+        <v>341</v>
+      </c>
+      <c r="K183" t="s">
+        <v>67</v>
+      </c>
+      <c r="L183" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>66</v>
+      </c>
+      <c r="B184" t="s">
+        <v>69</v>
+      </c>
+      <c r="C184" t="s">
+        <v>199</v>
+      </c>
+      <c r="D184">
+        <v>342</v>
+      </c>
+      <c r="K184" t="s">
+        <v>67</v>
+      </c>
+      <c r="L184" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>66</v>
+      </c>
+      <c r="B185" t="s">
+        <v>69</v>
+      </c>
+      <c r="C185" t="s">
+        <v>200</v>
+      </c>
+      <c r="D185">
+        <v>343</v>
+      </c>
+      <c r="K185" t="s">
+        <v>67</v>
+      </c>
+      <c r="L185" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>66</v>
+      </c>
+      <c r="B186" t="s">
+        <v>69</v>
+      </c>
+      <c r="C186" t="s">
+        <v>201</v>
+      </c>
+      <c r="D186">
+        <v>344</v>
+      </c>
+      <c r="K186" t="s">
+        <v>67</v>
+      </c>
+      <c r="L186" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>66</v>
+      </c>
+      <c r="B187" t="s">
+        <v>69</v>
+      </c>
+      <c r="C187" t="s">
+        <v>202</v>
+      </c>
+      <c r="D187">
+        <v>345</v>
+      </c>
+      <c r="K187" t="s">
+        <v>67</v>
+      </c>
+      <c r="L187" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>66</v>
+      </c>
+      <c r="B188" t="s">
+        <v>69</v>
+      </c>
+      <c r="C188" t="s">
+        <v>203</v>
+      </c>
+      <c r="D188">
+        <v>346</v>
+      </c>
+      <c r="K188" t="s">
+        <v>67</v>
+      </c>
+      <c r="L188" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>66</v>
+      </c>
+      <c r="B189" t="s">
+        <v>69</v>
+      </c>
+      <c r="C189" t="s">
+        <v>204</v>
+      </c>
+      <c r="D189">
+        <v>347</v>
+      </c>
+      <c r="K189" t="s">
+        <v>67</v>
+      </c>
+      <c r="L189" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>66</v>
+      </c>
+      <c r="B190" t="s">
+        <v>69</v>
+      </c>
+      <c r="C190" t="s">
+        <v>205</v>
+      </c>
+      <c r="D190">
+        <v>348</v>
+      </c>
+      <c r="K190" t="s">
+        <v>67</v>
+      </c>
+      <c r="L190" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>66</v>
+      </c>
+      <c r="B191" t="s">
+        <v>69</v>
+      </c>
+      <c r="C191" t="s">
+        <v>206</v>
+      </c>
+      <c r="D191">
+        <v>349</v>
+      </c>
+      <c r="K191" t="s">
+        <v>67</v>
+      </c>
+      <c r="L191" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>66</v>
+      </c>
+      <c r="B192" t="s">
+        <v>69</v>
+      </c>
+      <c r="C192" t="s">
+        <v>207</v>
+      </c>
+      <c r="D192">
+        <v>350</v>
+      </c>
+      <c r="K192" t="s">
+        <v>67</v>
+      </c>
+      <c r="L192" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>66</v>
+      </c>
+      <c r="B193" t="s">
+        <v>69</v>
+      </c>
+      <c r="C193" t="s">
+        <v>208</v>
+      </c>
+      <c r="D193">
+        <v>351</v>
+      </c>
+      <c r="K193" t="s">
+        <v>67</v>
+      </c>
+      <c r="L193" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>66</v>
+      </c>
+      <c r="B194" t="s">
+        <v>69</v>
+      </c>
+      <c r="C194" t="s">
+        <v>209</v>
+      </c>
+      <c r="D194">
+        <v>352</v>
+      </c>
+      <c r="K194" t="s">
+        <v>67</v>
+      </c>
+      <c r="L194" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>66</v>
+      </c>
+      <c r="B195" t="s">
+        <v>69</v>
+      </c>
+      <c r="C195" t="s">
+        <v>210</v>
+      </c>
+      <c r="D195">
+        <v>353</v>
+      </c>
+      <c r="K195" t="s">
+        <v>67</v>
+      </c>
+      <c r="L195" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>66</v>
+      </c>
+      <c r="B196" t="s">
+        <v>69</v>
+      </c>
+      <c r="C196" t="s">
+        <v>211</v>
+      </c>
+      <c r="D196">
+        <v>354</v>
+      </c>
+      <c r="K196" t="s">
+        <v>67</v>
+      </c>
+      <c r="L196" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>66</v>
+      </c>
+      <c r="B197" t="s">
+        <v>69</v>
+      </c>
+      <c r="C197" t="s">
+        <v>212</v>
+      </c>
+      <c r="D197">
+        <v>355</v>
+      </c>
+      <c r="K197" t="s">
+        <v>67</v>
+      </c>
+      <c r="L197" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>66</v>
+      </c>
+      <c r="B198" t="s">
+        <v>69</v>
+      </c>
+      <c r="C198" t="s">
+        <v>213</v>
+      </c>
+      <c r="D198">
+        <v>356</v>
+      </c>
+      <c r="K198" t="s">
+        <v>67</v>
+      </c>
+      <c r="L198" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>66</v>
+      </c>
+      <c r="B199" t="s">
+        <v>69</v>
+      </c>
+      <c r="C199" t="s">
+        <v>214</v>
+      </c>
+      <c r="D199">
+        <v>357</v>
+      </c>
+      <c r="K199" t="s">
+        <v>67</v>
+      </c>
+      <c r="L199" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>66</v>
+      </c>
+      <c r="B200" t="s">
+        <v>69</v>
+      </c>
+      <c r="C200" t="s">
+        <v>156</v>
+      </c>
+      <c r="D200">
+        <v>358</v>
+      </c>
+      <c r="K200" t="s">
+        <v>67</v>
+      </c>
+      <c r="L200" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>66</v>
+      </c>
+      <c r="B201" t="s">
+        <v>69</v>
+      </c>
+      <c r="C201" t="s">
+        <v>157</v>
+      </c>
+      <c r="D201">
+        <v>359</v>
+      </c>
+      <c r="K201" t="s">
+        <v>67</v>
+      </c>
+      <c r="L201" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>66</v>
+      </c>
+      <c r="B202" t="s">
+        <v>69</v>
+      </c>
+      <c r="C202" t="s">
+        <v>158</v>
+      </c>
+      <c r="D202">
+        <v>360</v>
+      </c>
+      <c r="K202" t="s">
+        <v>67</v>
+      </c>
+      <c r="L202" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>66</v>
+      </c>
+      <c r="B203" t="s">
+        <v>69</v>
+      </c>
+      <c r="C203" t="s">
+        <v>159</v>
+      </c>
+      <c r="D203">
+        <v>361</v>
+      </c>
+      <c r="K203" t="s">
+        <v>67</v>
+      </c>
+      <c r="L203" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>66</v>
+      </c>
+      <c r="B204" t="s">
+        <v>69</v>
+      </c>
+      <c r="C204" t="s">
+        <v>160</v>
+      </c>
+      <c r="D204">
+        <v>362</v>
+      </c>
+      <c r="K204" t="s">
+        <v>67</v>
+      </c>
+      <c r="L204" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>66</v>
+      </c>
+      <c r="B205" t="s">
+        <v>69</v>
+      </c>
+      <c r="C205" t="s">
+        <v>215</v>
+      </c>
+      <c r="D205">
+        <v>363</v>
+      </c>
+      <c r="K205" t="s">
+        <v>67</v>
+      </c>
+      <c r="L205" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>66</v>
+      </c>
+      <c r="B206" t="s">
+        <v>69</v>
+      </c>
+      <c r="C206" t="s">
+        <v>216</v>
+      </c>
+      <c r="D206">
+        <v>364</v>
+      </c>
+      <c r="K206" t="s">
+        <v>67</v>
+      </c>
+      <c r="L206" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>66</v>
+      </c>
+      <c r="B207" t="s">
+        <v>69</v>
+      </c>
+      <c r="C207" t="s">
+        <v>217</v>
+      </c>
+      <c r="D207">
+        <v>365</v>
+      </c>
+      <c r="K207" t="s">
+        <v>67</v>
+      </c>
+      <c r="L207" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>66</v>
+      </c>
+      <c r="B208" t="s">
+        <v>69</v>
+      </c>
+      <c r="C208" t="s">
+        <v>218</v>
+      </c>
+      <c r="D208">
+        <v>366</v>
+      </c>
+      <c r="K208" t="s">
+        <v>67</v>
+      </c>
+      <c r="L208" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>66</v>
+      </c>
+      <c r="B209" t="s">
+        <v>69</v>
+      </c>
+      <c r="C209" t="s">
+        <v>165</v>
+      </c>
+      <c r="D209">
+        <v>367</v>
+      </c>
+      <c r="K209" t="s">
+        <v>67</v>
+      </c>
+      <c r="L209" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>66</v>
+      </c>
+      <c r="B210" t="s">
+        <v>69</v>
+      </c>
+      <c r="C210" t="s">
+        <v>166</v>
+      </c>
+      <c r="D210">
+        <v>368</v>
+      </c>
+      <c r="K210" t="s">
+        <v>67</v>
+      </c>
+      <c r="L210" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>66</v>
+      </c>
+      <c r="B211" t="s">
+        <v>69</v>
+      </c>
+      <c r="C211" t="s">
+        <v>167</v>
+      </c>
+      <c r="D211">
+        <v>369</v>
+      </c>
+      <c r="K211" t="s">
+        <v>67</v>
+      </c>
+      <c r="L211" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>66</v>
+      </c>
+      <c r="B212" t="s">
+        <v>70</v>
+      </c>
+      <c r="C212" t="s">
+        <v>219</v>
+      </c>
+      <c r="D212">
+        <v>370</v>
+      </c>
+      <c r="K212" t="s">
+        <v>67</v>
+      </c>
+      <c r="L212" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>66</v>
+      </c>
+      <c r="B213" t="s">
+        <v>70</v>
+      </c>
+      <c r="C213" t="s">
+        <v>220</v>
+      </c>
+      <c r="D213">
+        <v>371</v>
+      </c>
+      <c r="K213" t="s">
+        <v>67</v>
+      </c>
+      <c r="L213" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>66</v>
+      </c>
+      <c r="B214" t="s">
+        <v>70</v>
+      </c>
+      <c r="C214" t="s">
+        <v>221</v>
+      </c>
+      <c r="D214">
+        <v>372</v>
+      </c>
+      <c r="K214" t="s">
+        <v>67</v>
+      </c>
+      <c r="L214" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>66</v>
+      </c>
+      <c r="B215" t="s">
+        <v>70</v>
+      </c>
+      <c r="C215" t="s">
+        <v>222</v>
+      </c>
+      <c r="D215">
+        <v>373</v>
+      </c>
+      <c r="K215" t="s">
+        <v>67</v>
+      </c>
+      <c r="L215" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>66</v>
+      </c>
+      <c r="B216" t="s">
+        <v>70</v>
+      </c>
+      <c r="C216" t="s">
+        <v>223</v>
+      </c>
+      <c r="D216">
+        <v>374</v>
+      </c>
+      <c r="K216" t="s">
+        <v>67</v>
+      </c>
+      <c r="L216" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>66</v>
+      </c>
+      <c r="B217" t="s">
+        <v>70</v>
+      </c>
+      <c r="C217" t="s">
+        <v>224</v>
+      </c>
+      <c r="D217">
+        <v>375</v>
+      </c>
+      <c r="K217" t="s">
+        <v>67</v>
+      </c>
+      <c r="L217" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>66</v>
+      </c>
+      <c r="B218" t="s">
+        <v>70</v>
+      </c>
+      <c r="C218" t="s">
+        <v>225</v>
+      </c>
+      <c r="D218">
+        <v>376</v>
+      </c>
+      <c r="K218" t="s">
+        <v>67</v>
+      </c>
+      <c r="L218" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>66</v>
+      </c>
+      <c r="B219" t="s">
+        <v>70</v>
+      </c>
+      <c r="C219" t="s">
+        <v>226</v>
+      </c>
+      <c r="D219">
+        <v>377</v>
+      </c>
+      <c r="K219" t="s">
+        <v>67</v>
+      </c>
+      <c r="L219" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>66</v>
+      </c>
+      <c r="B220" t="s">
+        <v>70</v>
+      </c>
+      <c r="C220" t="s">
+        <v>227</v>
+      </c>
+      <c r="D220">
+        <v>378</v>
+      </c>
+      <c r="K220" t="s">
+        <v>25</v>
+      </c>
+      <c r="L220" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>66</v>
+      </c>
+      <c r="B221" t="s">
+        <v>70</v>
+      </c>
+      <c r="C221" t="s">
+        <v>228</v>
+      </c>
+      <c r="D221">
+        <v>379</v>
+      </c>
+      <c r="K221" t="s">
+        <v>22</v>
+      </c>
+      <c r="L221" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>66</v>
+      </c>
+      <c r="B222" t="s">
+        <v>70</v>
+      </c>
+      <c r="C222" t="s">
+        <v>229</v>
+      </c>
+      <c r="D222">
+        <v>380</v>
+      </c>
+      <c r="K222" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="L222" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>66</v>
+      </c>
+      <c r="B223" t="s">
+        <v>70</v>
+      </c>
+      <c r="C223" t="s">
+        <v>230</v>
+      </c>
+      <c r="D223">
+        <v>381</v>
+      </c>
+      <c r="K223" t="s">
+        <v>26</v>
+      </c>
+      <c r="L223" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>66</v>
+      </c>
+      <c r="B224" t="s">
+        <v>70</v>
+      </c>
+      <c r="C224" t="s">
+        <v>231</v>
+      </c>
+      <c r="D224">
+        <v>382</v>
+      </c>
+      <c r="K224" t="s">
+        <v>26</v>
+      </c>
+      <c r="L224" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>66</v>
+      </c>
+      <c r="B225" t="s">
+        <v>70</v>
+      </c>
+      <c r="C225" t="s">
+        <v>232</v>
+      </c>
+      <c r="D225">
+        <v>383</v>
+      </c>
+      <c r="K225" t="s">
+        <v>26</v>
+      </c>
+      <c r="L225" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>66</v>
+      </c>
+      <c r="B226" t="s">
+        <v>70</v>
+      </c>
+      <c r="C226" t="s">
+        <v>233</v>
+      </c>
+      <c r="D226">
+        <v>384</v>
+      </c>
+      <c r="K226" t="s">
+        <v>26</v>
+      </c>
+      <c r="L226" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>66</v>
+      </c>
+      <c r="B227" t="s">
+        <v>70</v>
+      </c>
+      <c r="C227" t="s">
+        <v>234</v>
+      </c>
+      <c r="D227">
+        <v>385</v>
+      </c>
+      <c r="K227" t="s">
+        <v>26</v>
+      </c>
+      <c r="L227" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>66</v>
+      </c>
+      <c r="B228" t="s">
+        <v>70</v>
+      </c>
+      <c r="C228" t="s">
+        <v>235</v>
+      </c>
+      <c r="D228">
+        <v>386</v>
+      </c>
+      <c r="K228" t="s">
+        <v>26</v>
+      </c>
+      <c r="L228" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>66</v>
+      </c>
+      <c r="B229" t="s">
+        <v>70</v>
+      </c>
+      <c r="C229" t="s">
+        <v>236</v>
+      </c>
+      <c r="D229">
+        <v>387</v>
+      </c>
+      <c r="K229" t="s">
+        <v>26</v>
+      </c>
+      <c r="L229" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>66</v>
+      </c>
+      <c r="B230" t="s">
+        <v>70</v>
+      </c>
+      <c r="C230" t="s">
+        <v>237</v>
+      </c>
+      <c r="D230">
+        <v>388</v>
+      </c>
+      <c r="K230" t="s">
+        <v>26</v>
+      </c>
+      <c r="L230" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>66</v>
+      </c>
+      <c r="B231" t="s">
+        <v>70</v>
+      </c>
+      <c r="C231" t="s">
+        <v>238</v>
+      </c>
+      <c r="D231">
+        <v>389</v>
+      </c>
+      <c r="K231" t="s">
+        <v>26</v>
+      </c>
+      <c r="L231" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>66</v>
+      </c>
+      <c r="B232" t="s">
+        <v>70</v>
+      </c>
+      <c r="C232" t="s">
+        <v>239</v>
+      </c>
+      <c r="D232">
+        <v>390</v>
+      </c>
+      <c r="K232" t="s">
+        <v>26</v>
+      </c>
+      <c r="L232" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>66</v>
+      </c>
+      <c r="B233" t="s">
+        <v>70</v>
+      </c>
+      <c r="C233" t="s">
+        <v>240</v>
+      </c>
+      <c r="D233">
+        <v>391</v>
+      </c>
+      <c r="K233" t="s">
+        <v>26</v>
+      </c>
+      <c r="L233" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>66</v>
+      </c>
+      <c r="B234" t="s">
+        <v>70</v>
+      </c>
+      <c r="C234" t="s">
+        <v>241</v>
+      </c>
+      <c r="D234">
+        <v>392</v>
+      </c>
+      <c r="K234" t="s">
+        <v>26</v>
+      </c>
+      <c r="L234" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>66</v>
+      </c>
+      <c r="B235" t="s">
+        <v>70</v>
+      </c>
+      <c r="C235" t="s">
+        <v>242</v>
+      </c>
+      <c r="D235">
+        <v>393</v>
+      </c>
+      <c r="K235" t="s">
+        <v>26</v>
+      </c>
+      <c r="L235" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>66</v>
+      </c>
+      <c r="B236" t="s">
+        <v>70</v>
+      </c>
+      <c r="C236" t="s">
+        <v>243</v>
+      </c>
+      <c r="D236">
+        <v>394</v>
+      </c>
+      <c r="K236" t="s">
+        <v>26</v>
+      </c>
+      <c r="L236" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>66</v>
+      </c>
+      <c r="B237" t="s">
+        <v>70</v>
+      </c>
+      <c r="C237" t="s">
+        <v>244</v>
+      </c>
+      <c r="D237">
+        <v>395</v>
+      </c>
+      <c r="K237" t="s">
+        <v>26</v>
+      </c>
+      <c r="L237" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>66</v>
+      </c>
+      <c r="B238" t="s">
+        <v>70</v>
+      </c>
+      <c r="C238" t="s">
+        <v>245</v>
+      </c>
+      <c r="D238">
+        <v>396</v>
+      </c>
+      <c r="K238" t="s">
+        <v>26</v>
+      </c>
+      <c r="L238" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>66</v>
+      </c>
+      <c r="B239" t="s">
+        <v>70</v>
+      </c>
+      <c r="C239" t="s">
+        <v>246</v>
+      </c>
+      <c r="D239">
+        <v>397</v>
+      </c>
+      <c r="K239" t="s">
+        <v>26</v>
+      </c>
+      <c r="L239" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>66</v>
+      </c>
+      <c r="B240" t="s">
+        <v>70</v>
+      </c>
+      <c r="C240" t="s">
+        <v>247</v>
+      </c>
+      <c r="D240">
+        <v>398</v>
+      </c>
+      <c r="K240" t="s">
+        <v>26</v>
+      </c>
+      <c r="L240" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>66</v>
+      </c>
+      <c r="B241" t="s">
+        <v>70</v>
+      </c>
+      <c r="C241" t="s">
+        <v>248</v>
+      </c>
+      <c r="D241">
+        <v>399</v>
+      </c>
+      <c r="K241" t="s">
+        <v>26</v>
+      </c>
+      <c r="L241" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>66</v>
+      </c>
+      <c r="B242" t="s">
+        <v>70</v>
+      </c>
+      <c r="C242" t="s">
+        <v>249</v>
+      </c>
+      <c r="D242">
+        <v>400</v>
+      </c>
+      <c r="K242" t="s">
+        <v>26</v>
+      </c>
+      <c r="L242" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>66</v>
+      </c>
+      <c r="B243" t="s">
+        <v>70</v>
+      </c>
+      <c r="C243" t="s">
+        <v>250</v>
+      </c>
+      <c r="D243">
+        <v>401</v>
+      </c>
+      <c r="K243" t="s">
+        <v>26</v>
+      </c>
+      <c r="L243" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>66</v>
+      </c>
+      <c r="B244" t="s">
+        <v>70</v>
+      </c>
+      <c r="C244" t="s">
+        <v>251</v>
+      </c>
+      <c r="D244">
+        <v>402</v>
+      </c>
+      <c r="K244" t="s">
+        <v>78</v>
+      </c>
+      <c r="L244" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>66</v>
+      </c>
+      <c r="B245" t="s">
+        <v>70</v>
+      </c>
+      <c r="C245" t="s">
+        <v>252</v>
+      </c>
+      <c r="D245">
+        <v>403</v>
+      </c>
+      <c r="K245" t="s">
+        <v>77</v>
+      </c>
+      <c r="L245" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>66</v>
+      </c>
+      <c r="B246" t="s">
+        <v>71</v>
+      </c>
+      <c r="C246" t="s">
+        <v>253</v>
+      </c>
+      <c r="D246">
+        <v>404</v>
+      </c>
+      <c r="K246" t="s">
+        <v>68</v>
+      </c>
+      <c r="L246" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>66</v>
+      </c>
+      <c r="B247" t="s">
+        <v>71</v>
+      </c>
+      <c r="C247" t="s">
+        <v>254</v>
+      </c>
+      <c r="D247">
+        <v>405</v>
+      </c>
+      <c r="K247" t="s">
+        <v>68</v>
+      </c>
+      <c r="L247" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>66</v>
+      </c>
+      <c r="B248" t="s">
+        <v>71</v>
+      </c>
+      <c r="C248" t="s">
+        <v>255</v>
+      </c>
+      <c r="D248">
+        <v>406</v>
+      </c>
+      <c r="K248" t="s">
+        <v>68</v>
+      </c>
+      <c r="L248" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>66</v>
+      </c>
+      <c r="B249" t="s">
+        <v>71</v>
+      </c>
+      <c r="C249" t="s">
+        <v>256</v>
+      </c>
+      <c r="D249">
+        <v>407</v>
+      </c>
+      <c r="K249" t="s">
+        <v>68</v>
+      </c>
+      <c r="L249" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>66</v>
+      </c>
+      <c r="B250" t="s">
+        <v>71</v>
+      </c>
+      <c r="C250" t="s">
+        <v>257</v>
+      </c>
+      <c r="D250">
+        <v>408</v>
+      </c>
+      <c r="K250" t="s">
+        <v>68</v>
+      </c>
+      <c r="L250" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>66</v>
+      </c>
+      <c r="B251" t="s">
+        <v>71</v>
+      </c>
+      <c r="C251" t="s">
+        <v>258</v>
+      </c>
+      <c r="D251">
+        <v>409</v>
+      </c>
+      <c r="K251" t="s">
+        <v>68</v>
+      </c>
+      <c r="L251" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>66</v>
+      </c>
+      <c r="B252" t="s">
+        <v>71</v>
+      </c>
+      <c r="C252" t="s">
+        <v>259</v>
+      </c>
+      <c r="D252">
+        <v>410</v>
+      </c>
+      <c r="K252" t="s">
+        <v>68</v>
+      </c>
+      <c r="L252" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>66</v>
+      </c>
+      <c r="B253" t="s">
+        <v>71</v>
+      </c>
+      <c r="C253" t="s">
+        <v>260</v>
+      </c>
+      <c r="D253">
+        <v>411</v>
+      </c>
+      <c r="K253" t="s">
+        <v>68</v>
+      </c>
+      <c r="L253" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>66</v>
+      </c>
+      <c r="B254" t="s">
+        <v>71</v>
+      </c>
+      <c r="C254" t="s">
+        <v>261</v>
+      </c>
+      <c r="D254">
+        <v>412</v>
+      </c>
+      <c r="K254" t="s">
+        <v>68</v>
+      </c>
+      <c r="L254" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>66</v>
+      </c>
+      <c r="B255" t="s">
+        <v>71</v>
+      </c>
+      <c r="C255" t="s">
+        <v>262</v>
+      </c>
+      <c r="D255">
+        <v>413</v>
+      </c>
+      <c r="K255" t="s">
+        <v>68</v>
+      </c>
+      <c r="L255" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>66</v>
+      </c>
+      <c r="B256" t="s">
+        <v>71</v>
+      </c>
+      <c r="C256" t="s">
+        <v>263</v>
+      </c>
+      <c r="D256">
+        <v>414</v>
+      </c>
+      <c r="K256" t="s">
+        <v>68</v>
+      </c>
+      <c r="L256" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>66</v>
+      </c>
+      <c r="B257" t="s">
+        <v>71</v>
+      </c>
+      <c r="C257" t="s">
+        <v>264</v>
+      </c>
+      <c r="D257">
+        <v>415</v>
+      </c>
+      <c r="K257" t="s">
+        <v>68</v>
+      </c>
+      <c r="L257" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>66</v>
+      </c>
+      <c r="B258" t="s">
+        <v>71</v>
+      </c>
+      <c r="C258" t="s">
+        <v>265</v>
+      </c>
+      <c r="D258">
+        <v>416</v>
+      </c>
+      <c r="K258" t="s">
+        <v>68</v>
+      </c>
+      <c r="L258" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>66</v>
+      </c>
+      <c r="B259" t="s">
+        <v>71</v>
+      </c>
+      <c r="C259" t="s">
+        <v>266</v>
+      </c>
+      <c r="D259">
+        <v>417</v>
+      </c>
+      <c r="K259" t="s">
+        <v>68</v>
+      </c>
+      <c r="L259" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>66</v>
+      </c>
+      <c r="B260" t="s">
+        <v>71</v>
+      </c>
+      <c r="C260" t="s">
+        <v>267</v>
+      </c>
+      <c r="D260">
+        <v>418</v>
+      </c>
+      <c r="K260" t="s">
+        <v>68</v>
+      </c>
+      <c r="L260" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>66</v>
+      </c>
+      <c r="B261" t="s">
+        <v>71</v>
+      </c>
+      <c r="C261" t="s">
+        <v>268</v>
+      </c>
+      <c r="D261">
+        <v>419</v>
+      </c>
+      <c r="K261" t="s">
+        <v>68</v>
+      </c>
+      <c r="L261" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>66</v>
+      </c>
+      <c r="B262" t="s">
+        <v>71</v>
+      </c>
+      <c r="C262" t="s">
+        <v>269</v>
+      </c>
+      <c r="D262">
+        <v>420</v>
+      </c>
+      <c r="K262" t="s">
+        <v>68</v>
+      </c>
+      <c r="L262" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>66</v>
+      </c>
+      <c r="B263" t="s">
+        <v>71</v>
+      </c>
+      <c r="C263" t="s">
+        <v>270</v>
+      </c>
+      <c r="D263">
+        <v>421</v>
+      </c>
+      <c r="K263" t="s">
+        <v>68</v>
+      </c>
+      <c r="L263" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>66</v>
+      </c>
+      <c r="B264" t="s">
+        <v>71</v>
+      </c>
+      <c r="C264" t="s">
+        <v>271</v>
+      </c>
+      <c r="D264">
+        <v>422</v>
+      </c>
+      <c r="K264" t="s">
+        <v>68</v>
+      </c>
+      <c r="L264" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>66</v>
+      </c>
+      <c r="B265" t="s">
+        <v>71</v>
+      </c>
+      <c r="C265" t="s">
+        <v>272</v>
+      </c>
+      <c r="D265">
+        <v>423</v>
+      </c>
+      <c r="K265" t="s">
+        <v>68</v>
+      </c>
+      <c r="L265" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>66</v>
+      </c>
+      <c r="B266" t="s">
+        <v>71</v>
+      </c>
+      <c r="C266" t="s">
+        <v>273</v>
+      </c>
+      <c r="D266">
+        <v>424</v>
+      </c>
+      <c r="K266" t="s">
+        <v>68</v>
+      </c>
+      <c r="L266" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>66</v>
+      </c>
+      <c r="B267" t="s">
+        <v>71</v>
+      </c>
+      <c r="C267" t="s">
+        <v>274</v>
+      </c>
+      <c r="D267">
+        <v>425</v>
+      </c>
+      <c r="K267" t="s">
+        <v>68</v>
+      </c>
+      <c r="L267" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>66</v>
+      </c>
+      <c r="B268" t="s">
+        <v>71</v>
+      </c>
+      <c r="C268" t="s">
+        <v>275</v>
+      </c>
+      <c r="D268">
+        <v>426</v>
+      </c>
+      <c r="K268" t="s">
+        <v>68</v>
+      </c>
+      <c r="L268" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>66</v>
+      </c>
+      <c r="B269" t="s">
+        <v>71</v>
+      </c>
+      <c r="C269" t="s">
+        <v>276</v>
+      </c>
+      <c r="D269">
+        <v>427</v>
+      </c>
+      <c r="K269" t="s">
+        <v>68</v>
+      </c>
+      <c r="L269" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>66</v>
+      </c>
+      <c r="B270" t="s">
+        <v>71</v>
+      </c>
+      <c r="C270" t="s">
+        <v>277</v>
+      </c>
+      <c r="D270">
+        <v>428</v>
+      </c>
+      <c r="K270" t="s">
+        <v>68</v>
+      </c>
+      <c r="L270" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>66</v>
+      </c>
+      <c r="B271" t="s">
+        <v>71</v>
+      </c>
+      <c r="C271" t="s">
+        <v>278</v>
+      </c>
+      <c r="D271">
+        <v>429</v>
+      </c>
+      <c r="K271" t="s">
+        <v>68</v>
+      </c>
+      <c r="L271" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>66</v>
+      </c>
+      <c r="B272" t="s">
+        <v>71</v>
+      </c>
+      <c r="C272" t="s">
+        <v>279</v>
+      </c>
+      <c r="D272">
+        <v>430</v>
+      </c>
+      <c r="K272" t="s">
+        <v>68</v>
+      </c>
+      <c r="L272" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>66</v>
+      </c>
+      <c r="B273" t="s">
+        <v>71</v>
+      </c>
+      <c r="C273" t="s">
+        <v>280</v>
+      </c>
+      <c r="D273">
+        <v>431</v>
+      </c>
+      <c r="K273" t="s">
+        <v>68</v>
+      </c>
+      <c r="L273" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>66</v>
+      </c>
+      <c r="B274" t="s">
+        <v>71</v>
+      </c>
+      <c r="C274" t="s">
+        <v>281</v>
+      </c>
+      <c r="D274">
+        <v>432</v>
+      </c>
+      <c r="K274" t="s">
+        <v>68</v>
+      </c>
+      <c r="L274" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>66</v>
+      </c>
+      <c r="B275" t="s">
+        <v>71</v>
+      </c>
+      <c r="C275" t="s">
+        <v>282</v>
+      </c>
+      <c r="D275">
+        <v>433</v>
+      </c>
+      <c r="K275" t="s">
+        <v>68</v>
+      </c>
+      <c r="L275" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>66</v>
+      </c>
+      <c r="B276" t="s">
+        <v>71</v>
+      </c>
+      <c r="C276" t="s">
+        <v>283</v>
+      </c>
+      <c r="D276">
+        <v>434</v>
+      </c>
+      <c r="K276" t="s">
+        <v>68</v>
+      </c>
+      <c r="L276" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>66</v>
+      </c>
+      <c r="B277" t="s">
+        <v>72</v>
+      </c>
+      <c r="C277" t="s">
+        <v>72</v>
+      </c>
+      <c r="D277">
+        <v>435</v>
+      </c>
+      <c r="K277" t="s">
+        <v>68</v>
+      </c>
+      <c r="L277" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>66</v>
+      </c>
+      <c r="B278" t="s">
+        <v>72</v>
+      </c>
+      <c r="C278" t="s">
+        <v>284</v>
+      </c>
+      <c r="D278">
+        <v>436</v>
+      </c>
+      <c r="K278" t="s">
+        <v>68</v>
+      </c>
+      <c r="L278" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>66</v>
+      </c>
+      <c r="B279" t="s">
+        <v>72</v>
+      </c>
+      <c r="C279" t="s">
+        <v>285</v>
+      </c>
+      <c r="D279">
+        <v>437</v>
+      </c>
+      <c r="K279" t="s">
+        <v>68</v>
+      </c>
+      <c r="L279" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>66</v>
+      </c>
+      <c r="B280" t="s">
+        <v>72</v>
+      </c>
+      <c r="C280" t="s">
+        <v>286</v>
+      </c>
+      <c r="D280">
+        <v>438</v>
+      </c>
+      <c r="K280" t="s">
+        <v>68</v>
+      </c>
+      <c r="L280" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>66</v>
+      </c>
+      <c r="B281" t="s">
+        <v>72</v>
+      </c>
+      <c r="C281" t="s">
+        <v>287</v>
+      </c>
+      <c r="D281">
+        <v>439</v>
+      </c>
+      <c r="K281" t="s">
+        <v>68</v>
+      </c>
+      <c r="L281" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>66</v>
+      </c>
+      <c r="B282" t="s">
+        <v>72</v>
+      </c>
+      <c r="C282" t="s">
+        <v>288</v>
+      </c>
+      <c r="D282">
+        <v>440</v>
+      </c>
+      <c r="K282" t="s">
+        <v>68</v>
+      </c>
+      <c r="L282" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>66</v>
+      </c>
+      <c r="B283" t="s">
+        <v>72</v>
+      </c>
+      <c r="C283" t="s">
+        <v>289</v>
+      </c>
+      <c r="D283">
+        <v>441</v>
+      </c>
+      <c r="K283" t="s">
+        <v>68</v>
+      </c>
+      <c r="L283" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>66</v>
+      </c>
+      <c r="B284" t="s">
+        <v>72</v>
+      </c>
+      <c r="C284" t="s">
+        <v>290</v>
+      </c>
+      <c r="D284">
+        <v>442</v>
+      </c>
+      <c r="K284" t="s">
+        <v>68</v>
+      </c>
+      <c r="L284" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>66</v>
+      </c>
+      <c r="B285" t="s">
+        <v>72</v>
+      </c>
+      <c r="C285" t="s">
+        <v>291</v>
+      </c>
+      <c r="D285">
+        <v>443</v>
+      </c>
+      <c r="K285" t="s">
+        <v>68</v>
+      </c>
+      <c r="L285" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>66</v>
+      </c>
+      <c r="B286" t="s">
+        <v>72</v>
+      </c>
+      <c r="C286" t="s">
+        <v>292</v>
+      </c>
+      <c r="D286">
+        <v>444</v>
+      </c>
+      <c r="K286" t="s">
+        <v>68</v>
+      </c>
+      <c r="L286" t="s">
+        <v>146</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D42">
-    <sortCondition ref="A2:A42"/>
-    <sortCondition ref="B2:B42"/>
-    <sortCondition ref="C2:C42"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K2:L286">
+    <sortCondition ref="K2:K286"/>
+    <sortCondition ref="L2:L286"/>
   </sortState>
-  <conditionalFormatting sqref="C1:C1048576">
+  <conditionalFormatting sqref="C63:C1048576 C1:C42">
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L63:L1048576 L1:L42">
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D286">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
